--- a/results/job_matches_2026-07-31.xlsx
+++ b/results/job_matches_2026-07-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,25 +643,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Java Developer - Child Support Management System</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Strategic Mindz LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>IAM, RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Vertex AI, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,19 +671,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=817df956fbf694bd</t>
+          <t>https://www.indeed.com/viewjob?jk=751ce7cf6c298548</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Novanta</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IAM, RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Vertex AI, Hadoop, Hive, Spark</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Oracle, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=751ce7cf6c298548</t>
+          <t>https://www.indeed.com/viewjob?jk=1d84674d8dbd92bd</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Applied AI SRE III - PxE GPS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Novanta</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Oracle, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, Splunk, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d84674d8dbd92bd</t>
+          <t>https://www.indeed.com/viewjob?jk=d84df72ea9532c51</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Technical Solution Architect</t>
+          <t>Applied AI SRE III - PxE GPS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sparksoft Corporation</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, Splunk, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb08bdb737e91628</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c8966b4d59c6b1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Applied AI SRE III - PxE GPS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS, ECS</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, Splunk, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3bc1c0882246fa5</t>
+          <t>https://www.indeed.com/viewjob?jk=62830a371d1e64c4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DataOps Engineer</t>
+          <t>Applied AI SRE III - PxE GPS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Linstarsolution corporation</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, Splunk, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be67238d1b6a44a</t>
+          <t>https://www.indeed.com/viewjob?jk=7b49a235e6405f16</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Applied AI SRE III - PxE GPS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, Splunk, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b44d49984ac43ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=1135d93688985c7c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior DotNET Developer - Child Support Management System</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Strategic Mindz LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Blob Storage, Scala, Kafka, SQL Server, PostgreSQL, Splunk</t>
+          <t>AWS, EMR, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS, ECS</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1474978de0278b7b</t>
+          <t>https://www.indeed.com/viewjob?jk=e3bc1c0882246fa5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>DataOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BakerHostetler</t>
+          <t>Linstarsolution corporation</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, Medallion Architecture, Spark, Scala</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e610a35113b8a37</t>
+          <t>https://www.indeed.com/viewjob?jk=3be67238d1b6a44a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Cloud DevOps Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Michael Baker International</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8279b19004b6546d</t>
+          <t>https://www.indeed.com/viewjob?jk=b44d49984ac43ef9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS, Databricks, Python</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BakerHostetler</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, Medallion Architecture, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=118a88261f4a95ca</t>
+          <t>https://www.indeed.com/viewjob?jk=6e610a35113b8a37</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer III - C# / Java</t>
+          <t>Senior Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Michael Baker International</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=735136a340f06328</t>
+          <t>https://www.indeed.com/viewjob?jk=8279b19004b6546d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Power BI Data Analyst</t>
+          <t>Business Intelligence Engineer II, Procurement, Real Estate &amp; Facilities Analytics</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Loffler Companies, Inc.</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, Scala, SQL Server, Star Schema</t>
+          <t>AWS, Athena, S3, RDS, Hadoop, Hive, Spark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d521ef740f60ce71</t>
+          <t>https://www.indeed.com/viewjob?jk=a4f8c0cf0c31b9e0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - C# / Java</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The Museum of Modern Art</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bcc4b2fa6c73536</t>
+          <t>https://www.indeed.com/viewjob?jk=735136a340f06328</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Microsoft Certified Power Platform Solution Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>j. anukem &amp; associates</t>
+          <t>The Museum of Modern Art</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, NoSQL, Power BI</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9829e7244bb5e65a</t>
+          <t>https://www.indeed.com/viewjob?jk=9bcc4b2fa6c73536</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f01a424e09b95ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=ebbb3368fcab6386</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer - Onboarding</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sardine</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, dbt, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eafe0da0cb06f132</t>
+          <t>https://www.indeed.com/viewjob?jk=f01a424e09b95ee6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Business Data Architect</t>
+          <t>Data Engineer - Onboarding</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Sardine</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Spark Streaming</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd28b1da9cfe4d40</t>
+          <t>https://www.indeed.com/viewjob?jk=eafe0da0cb06f132</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Business Data Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Spark Streaming</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=235882076ff46707</t>
+          <t>https://www.indeed.com/viewjob?jk=cd28b1da9cfe4d40</t>
         </is>
       </c>
     </row>
@@ -1343,52 +1343,52 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Engineer, AI Strategy and Solutions</t>
+          <t>Production Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Universal Creative</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MongoDB, ETL, Jenkins, Maven, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6766b0436a9e52df</t>
+          <t>https://www.indeed.com/viewjob?jk=50cc2032a060fc77</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Production Data Engineer</t>
+          <t>AI, AWS DevOps, Java/Python Software Engineer III</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MongoDB, ETL, Jenkins, Maven, Terraform</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50cc2032a060fc77</t>
+          <t>https://www.indeed.com/viewjob?jk=65068caf46548141</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI, AWS DevOps, Java/Python Software Engineer III</t>
+          <t>Senior Data Engineer - Databricks (No Sponsorship Available)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Heritage Construction + Materials</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65068caf46548141</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8c3d75cc5a59c9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Databricks (No Sponsorship Available)</t>
+          <t>Senior AI/ML Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Heritage Construction + Materials</t>
+          <t>Public Storage</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, dbt, MLflow</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f8c3d75cc5a59c9</t>
+          <t>https://www.indeed.com/viewjob?jk=d7493eab3654bd62</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior AI/ML Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Public Storage</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, dbt, MLflow</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Kafka, Oracle, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7493eab3654bd62</t>
+          <t>https://www.indeed.com/viewjob?jk=e5685d1301702faa</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III (Agentic AI/Java/AWS/Microservices)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Kafka, Oracle, PostgreSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5685d1301702faa</t>
+          <t>https://www.indeed.com/viewjob?jk=41fb8ee0e0bf2d91</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer III (Agentic AI/Java/AWS/Microservices)</t>
+          <t>Consulting Data Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, CI/CD</t>
+          <t>AWS, Glue, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41fb8ee0e0bf2d91</t>
+          <t>https://www.indeed.com/viewjob?jk=aff47d92a692d4c3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Consulting Data Architect</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aff47d92a692d4c3</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e3f52aa2a3ab7a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Cloud Engineer Senior</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>Freddie Mac</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Athena, S3, API Gateway, IAM, RDS, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e3f52aa2a3ab7a</t>
+          <t>https://www.indeed.com/viewjob?jk=ca6f5d8776368811</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cloud Engineer Senior</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Freddie Mac</t>
+          <t>Berkshire Hathaway GUARD Insurance Companies</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, API Gateway, IAM, RDS, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca6f5d8776368811</t>
+          <t>https://www.indeed.com/viewjob?jk=6d44e48661eb7c09</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Transformation Data Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway GUARD Insurance Companies</t>
+          <t>Patriot Bank, N.A.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d44e48661eb7c09</t>
+          <t>https://www.indeed.com/viewjob?jk=7777dc92cdf89b5a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Transformation Data Architect</t>
+          <t>NYS ITS Expert Software Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Patriot Bank, N.A.</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Menands, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7777dc92cdf89b5a</t>
+          <t>https://www.indeed.com/viewjob?jk=3578a6d785ac61e9</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Developer - Automation Core</t>
+          <t>Sr Dir Software - Data Platform Engineer - Minneapolis, MN</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Regeneron</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tarrytown, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Data Modeling, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00e334c03bdbb374</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8fa88f7e3fd0c2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Analyst (Hybrid - Madison or Austin)</t>
+          <t>Software Development Engineer II - Gen AI and Innovation Team</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Snowflake, Data Modeling, dbt, Power BI</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=289d005fb52fdb68</t>
+          <t>https://www.indeed.com/viewjob?jk=93f5da6a90e11da1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr Dir Software - Data Platform Engineer - Minneapolis, MN</t>
+          <t>Senior Data Analyst (Hybrid - Madison or Austin)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Snowflake, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8fa88f7e3fd0c2</t>
+          <t>https://www.indeed.com/viewjob?jk=289d005fb52fdb68</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - Gen AI and Innovation Team</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, S3, Azure, Databricks, Blob Storage, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93f5da6a90e11da1</t>
+          <t>https://www.indeed.com/viewjob?jk=70a69ee2362e8f4b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Blob Storage, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70a69ee2362e8f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=87b420bcd07d16a3</t>
         </is>
       </c>
     </row>
@@ -2078,17 +2078,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SAP S/4HANA MMPP Functional Consultant</t>
+          <t>Cloud SME X2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>California City, CA, US USA</t>
+          <t>Juno Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b51f21983ae125e</t>
+          <t>https://www.indeed.com/viewjob?jk=5a558c1d3bd32ae5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cloud SME X2</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>Virta Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Juno Beach, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD</t>
+          <t>AWS, ECS, RDS, Google Cloud Platform, BigQuery, Scala, dbt, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a558c1d3bd32ae5</t>
+          <t>https://www.indeed.com/viewjob?jk=671761ff02fb6ab9</t>
         </is>
       </c>
     </row>
@@ -2358,17 +2358,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>AI Foundational Model Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,42 +2376,42 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9708ccf9ee0f5af2</t>
+          <t>https://www.indeed.com/viewjob?jk=376d725617b0f2aa</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AI Foundational Model Engineer</t>
+          <t>Senior Full-Stack Engineer (Go/Typescript)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Plan A Technologies</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=376d725617b0f2aa</t>
+          <t>https://www.indeed.com/viewjob?jk=73913eba01c47259</t>
         </is>
       </c>
     </row>
@@ -2498,17 +2498,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer - ML Infrastructure</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Epsilon Labs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, MLOps, Docker</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5b12d9efc6c6a98</t>
+          <t>https://www.indeed.com/viewjob?jk=fa70f2dbee018b7c</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer, CX</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff73ed78b417b14</t>
+          <t>https://www.indeed.com/viewjob?jk=6b763786ad2e38b4</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer-Data Platform &amp; Analytics</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b950c881dbe97c6</t>
+          <t>https://www.indeed.com/viewjob?jk=e5c47c6ff1b8d763</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Salesforce Development Engineer II</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2bd0abe4afa5b39</t>
+          <t>https://www.indeed.com/viewjob?jk=1176d370cb1ec66e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Hightower Advisors</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, Snowflake, DynamoDB</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0d0534e87a93a57</t>
+          <t>https://www.indeed.com/viewjob?jk=f7dbdd0593036388</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Integrations Engineer I</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Kendra Scott</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, NoSQL, Docker, Kubernetes</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58b78bbfcdcc6779</t>
+          <t>https://www.indeed.com/viewjob?jk=3ef6dc42abc1b379</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer - SQL and Snowflake</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c79cad4a6a280f3</t>
+          <t>https://www.indeed.com/viewjob?jk=8dfe58cb3ddb0d22</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Analytics Engineer, Day Shift, Strategic Analytics</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Adventist HealthCare</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>EMR, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc034fd3ef508e12</t>
+          <t>https://www.indeed.com/viewjob?jk=5bdd6daf0b2fd71e</t>
         </is>
       </c>
     </row>
@@ -2783,20 +2783,20 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Reach Financial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, Tableau, CI/CD</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,67 +2806,67 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62588f4999e63221</t>
+          <t>https://www.indeed.com/viewjob?jk=0e5c22da5a84813b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Palantir Foundry</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d5ca9632878562c</t>
+          <t>https://www.indeed.com/viewjob?jk=984dc7e3ef8ef833</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Python Developer Senior</t>
+          <t>Software Engineer - ML Infrastructure</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>Epsilon Labs</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Spark, PySpark, Scala, Dask, Polars, PostgreSQL, Data Modeling, ETL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, MLOps, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,67 +2876,67 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1b165e2a50dc910</t>
+          <t>https://www.indeed.com/viewjob?jk=e5b12d9efc6c6a98</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AI Software Architect</t>
+          <t>Data Engineer-Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Park Place Technologies</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Highland Heights, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, MLOps, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5333ce5a9b1f0a9f</t>
+          <t>https://www.indeed.com/viewjob?jk=5b950c881dbe97c6</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Python Engineer, Financial Data Platform &amp; Integrations</t>
+          <t>Senior Developer - Information Technology</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Cardiff</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, Snowflake, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, CI/CD, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44c5ea64ad488307</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3e76c7cba2c5ef</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Ecommerce Web Applications (US/Canada)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CSC Generation</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a55d577c0fda86f2</t>
+          <t>https://www.indeed.com/viewjob?jk=0fd3a77f9dc14549</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Salesforce Development Engineer II</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, Oracle, MySQL, NoSQL, ETL, CI/CD, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec9b8320959ff15</t>
+          <t>https://www.indeed.com/viewjob?jk=b2bd0abe4afa5b39</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Remote) - Radiology</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Washington University in St. Louis</t>
+          <t>Hightower Advisors</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Terraform, Git, Bitbucket</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e445dc5779186f6</t>
+          <t>https://www.indeed.com/viewjob?jk=c0d0534e87a93a57</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Plan A Technologies</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, S3, ECS, RDS, Scala, DataOps, CI/CD, Terraform, Docker, CloudWatch</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08083d178d541b5c</t>
+          <t>https://www.indeed.com/viewjob?jk=d47e70c4d7b465c7</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AI Engineer — GTM Analytics</t>
+          <t>Senior Integrations Engineer I</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Kendra Scott</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Databricks Lakehouse, ELT, dbt, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f9697dd941d556f</t>
+          <t>https://www.indeed.com/viewjob?jk=58b78bbfcdcc6779</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Specialist, Data Engineer - SQL and Snowflake</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Spark, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=642a2e2441a31d20</t>
+          <t>https://www.indeed.com/viewjob?jk=5c79cad4a6a280f3</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>GenAI Python Systems Engineer – Experienced Associate</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Spark, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Terraform, AWS CloudFormation, Docker, Python</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4555ba9a9f5693be</t>
+          <t>https://www.indeed.com/viewjob?jk=092180f6fccecac1</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Analytics Engineer, Day Shift, Strategic Analytics</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Adventist HealthCare</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Spark, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>EMR, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94a8a92e1381b54a</t>
+          <t>https://www.indeed.com/viewjob?jk=fc034fd3ef508e12</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Reach Financial</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Spark, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2413e7f250d00cb8</t>
+          <t>https://www.indeed.com/viewjob?jk=62588f4999e63221</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data Engineer - Palantir Foundry</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,17 +3286,437 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Spark, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e1faeaec512b702</t>
+          <t>https://www.indeed.com/viewjob?jk=0d5ca9632878562c</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Senior UX Software Engineer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>GRVTY</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Cambridge, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=188385fe594d1176</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Sr. Fullstack Developer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>ExxonMobil</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Spring, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b803553ffc2f5e53</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Python Developer Senior</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Technology Ventures</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Spark, PySpark, Scala, Dask, Polars, PostgreSQL, Data Modeling, ETL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1b165e2a50dc910</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>AI Software Architect</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Park Place Technologies</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Highland Heights, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, MLOps, CI/CD, Azure DevOps, Git, Python</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5333ce5a9b1f0a9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>IT Systems Engineer III</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Delan Associates, Inc</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Palm Beach Gardens, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, PostgreSQL, ETL, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=371bf76528aae202</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Ecommerce Web Applications (US/Canada)</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>CSC Generation</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a55d577c0fda86f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Minnetonka, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Kafka, Oracle, MySQL, NoSQL, ETL, CI/CD, GitHub Actions, Docker</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ec9b8320959ff15</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=08083d178d541b5c</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Remote) - Radiology</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Washington University in St. Louis</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Medallion Architecture, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Terraform, Git, Bitbucket</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e445dc5779186f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>AI Engineer — GTM Analytics</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Databricks Lakehouse, ELT, dbt, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f9697dd941d556f</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Python Engineer, Financial Data Platform &amp; Integrations</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Cardiff</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, Snowflake, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=44c5ea64ad488307</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer III</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c84476dc78d41318</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-31.xlsx
+++ b/results/job_matches_2026-07-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer II, Procurement, Real Estate &amp; Facilities Analytics</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, RDS, Hadoop, Hive, Spark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4f8c0cf0c31b9e0</t>
+          <t>https://www.indeed.com/viewjob?jk=dba8335e79adaef9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer III - C# / Java</t>
+          <t>Business Intelligence Engineer II, Procurement, Real Estate &amp; Facilities Analytics</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,42 +1116,42 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Athena, S3, RDS, Hadoop, Hive, Spark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=735136a340f06328</t>
+          <t>https://www.indeed.com/viewjob?jk=a4f8c0cf0c31b9e0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - C# / Java</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The Museum of Modern Art</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,19 +1161,19 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bcc4b2fa6c73536</t>
+          <t>https://www.indeed.com/viewjob?jk=735136a340f06328</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>The Museum of Modern Art</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebbb3368fcab6386</t>
+          <t>https://www.indeed.com/viewjob?jk=9bcc4b2fa6c73536</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f01a424e09b95ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=ebbb3368fcab6386</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer - Onboarding</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sardine</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, dbt, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eafe0da0cb06f132</t>
+          <t>https://www.indeed.com/viewjob?jk=f01a424e09b95ee6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Business Data Architect</t>
+          <t>Data Engineer - Onboarding</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Sardine</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Spark Streaming</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd28b1da9cfe4d40</t>
+          <t>https://www.indeed.com/viewjob?jk=eafe0da0cb06f132</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. SW Engineer</t>
+          <t>Business Data Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD, Terraform</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Spark Streaming</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20a004e42eab6632</t>
+          <t>https://www.indeed.com/viewjob?jk=cd28b1da9cfe4d40</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Production Data Engineer</t>
+          <t>Sr. SW Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MongoDB, ETL, Jenkins, Maven, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50cc2032a060fc77</t>
+          <t>https://www.indeed.com/viewjob?jk=20a004e42eab6632</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI, AWS DevOps, Java/Python Software Engineer III</t>
+          <t>Production Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MongoDB, ETL, Jenkins, Maven, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65068caf46548141</t>
+          <t>https://www.indeed.com/viewjob?jk=50cc2032a060fc77</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Databricks (No Sponsorship Available)</t>
+          <t>AI, AWS DevOps, Java/Python Software Engineer III</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Heritage Construction + Materials</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f8c3d75cc5a59c9</t>
+          <t>https://www.indeed.com/viewjob?jk=65068caf46548141</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior AI/ML Data Engineer</t>
+          <t>Senior Data Engineer - Databricks (No Sponsorship Available)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Public Storage</t>
+          <t>Heritage Construction + Materials</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, dbt, MLflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7493eab3654bd62</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8c3d75cc5a59c9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI/ML Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Public Storage</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Kafka, Oracle, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, dbt, MLflow</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5685d1301702faa</t>
+          <t>https://www.indeed.com/viewjob?jk=d7493eab3654bd62</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer III (Agentic AI/Java/AWS/Microservices)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Kafka, Oracle, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41fb8ee0e0bf2d91</t>
+          <t>https://www.indeed.com/viewjob?jk=e5685d1301702faa</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Consulting Data Architect</t>
+          <t>Software Engineer III (Agentic AI/Java/AWS/Microservices)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aff47d92a692d4c3</t>
+          <t>https://www.indeed.com/viewjob?jk=41fb8ee0e0bf2d91</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e3f52aa2a3ab7a</t>
+          <t>https://www.indeed.com/viewjob?jk=e9d72ec9cbbadf7a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cloud Engineer Senior</t>
+          <t>Consulting Data Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Freddie Mac</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, API Gateway, IAM, RDS, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca6f5d8776368811</t>
+          <t>https://www.indeed.com/viewjob?jk=aff47d92a692d4c3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway GUARD Insurance Companies</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d44e48661eb7c09</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e3f52aa2a3ab7a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Transformation Data Architect</t>
+          <t>Cloud Engineer Senior</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Patriot Bank, N.A.</t>
+          <t>Freddie Mac</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Athena, S3, API Gateway, IAM, RDS, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7777dc92cdf89b5a</t>
+          <t>https://www.indeed.com/viewjob?jk=ca6f5d8776368811</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>NYS ITS Expert Software Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>Berkshire Hathaway GUARD Insurance Companies</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Menands, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3578a6d785ac61e9</t>
+          <t>https://www.indeed.com/viewjob?jk=6d44e48661eb7c09</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr Dir Software - Data Platform Engineer - Minneapolis, MN</t>
+          <t>Senior Data Transformation Data Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Patriot Bank, N.A.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8fa88f7e3fd0c2</t>
+          <t>https://www.indeed.com/viewjob?jk=7777dc92cdf89b5a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - Gen AI and Innovation Team</t>
+          <t>NYS ITS Expert Software Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Menands, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93f5da6a90e11da1</t>
+          <t>https://www.indeed.com/viewjob?jk=3578a6d785ac61e9</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Analyst (Hybrid - Madison or Austin)</t>
+          <t>Sr Dir Software - Data Platform Engineer - Minneapolis, MN</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Snowflake, Data Modeling, dbt, Power BI</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=289d005fb52fdb68</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8fa88f7e3fd0c2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Development Engineer II - Gen AI and Innovation Team</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Blob Storage, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70a69ee2362e8f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=93f5da6a90e11da1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Analyst (Hybrid - Madison or Austin)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
+          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Snowflake, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87b420bcd07d16a3</t>
+          <t>https://www.indeed.com/viewjob?jk=289d005fb52fdb68</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Site Reliability Engineers</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Careers Inc</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, S3, Azure, Databricks, Blob Storage, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22d91b3a0cb9046d</t>
+          <t>https://www.indeed.com/viewjob?jk=70a69ee2362e8f4b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python, Databricks and AWS</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse</t>
+          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbfe0afb6a8f866d</t>
+          <t>https://www.indeed.com/viewjob?jk=87b420bcd07d16a3</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior CloudOps Engineer</t>
+          <t>Site Reliability Engineers</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Domo, Inc.</t>
+          <t>Careers Inc</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c47bac900059df12</t>
+          <t>https://www.indeed.com/viewjob?jk=22d91b3a0cb9046d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Associate Data Engineer (Remote)</t>
+          <t>Software Engineer III - Python, Databricks and AWS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Crum &amp; Forster</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Kafka, Snowflake, ETL</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2b8d579584394d6</t>
+          <t>https://www.indeed.com/viewjob?jk=cbfe0afb6a8f866d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cloud SME X2</t>
+          <t>Senior CloudOps Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>Domo, Inc.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Juno Beach, FL, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a558c1d3bd32ae5</t>
+          <t>https://www.indeed.com/viewjob?jk=c47bac900059df12</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Cloud SME X2</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Virta Health</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Juno Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Google Cloud Platform, BigQuery, Scala, dbt, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=671761ff02fb6ab9</t>
+          <t>https://www.indeed.com/viewjob?jk=5a558c1d3bd32ae5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer (Angular + .NET, Azure)</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Indiana Donor Network</t>
+          <t>Virta Health</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Google Cloud Platform, BigQuery, Scala, dbt, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e254843359a11bda</t>
+          <t>https://www.indeed.com/viewjob?jk=671761ff02fb6ab9</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer - Early Career - Landmark</t>
+          <t>Software Engineer (Angular + .NET, Azure)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Halliburton</t>
+          <t>Indiana Donor Network</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2854756df3635191</t>
+          <t>https://www.indeed.com/viewjob?jk=e254843359a11bda</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer, IT Software</t>
+          <t>Software Engineer - Early Career - Landmark</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Halliburton</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f18b9877a4bf7ae</t>
+          <t>https://www.indeed.com/viewjob?jk=2854756df3635191</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior BI Engineer</t>
+          <t>Sr Associate Engineer, IT Software</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Daisy Brand</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91b1714cc80b634c</t>
+          <t>https://www.indeed.com/viewjob?jk=9f18b9877a4bf7ae</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior BI Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Daisy Brand</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc1820a549077871</t>
+          <t>https://www.indeed.com/viewjob?jk=91b1714cc80b634c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Backend Engineer _ AI Gateway</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Linstarsolution corporation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40978ef369a5ee61</t>
+          <t>https://www.indeed.com/viewjob?jk=bc1820a549077871</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI Foundational Model Engineer</t>
+          <t>Backend Engineer _ AI Gateway</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Linstarsolution corporation</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=376d725617b0f2aa</t>
+          <t>https://www.indeed.com/viewjob?jk=40978ef369a5ee61</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer (Go/Typescript)</t>
+          <t>AI Foundational Model Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Plan A Technologies</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73913eba01c47259</t>
+          <t>https://www.indeed.com/viewjob?jk=376d725617b0f2aa</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Promotions</t>
+          <t>Senior Full-Stack Engineer (Go/Typescript)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>Plan A Technologies</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b535237436c3096a</t>
+          <t>https://www.indeed.com/viewjob?jk=73913eba01c47259</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data and AI</t>
+          <t>Senior Software Engineer, Promotions</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Cisive</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Scala, NoSQL, Data Modeling, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=743af78e2a52e54b</t>
+          <t>https://www.indeed.com/viewjob?jk=b535237436c3096a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Engineer, Data and AI</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Cisive</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>Azure, Databricks, Spark, Scala, NoSQL, Data Modeling, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,14 +2526,14 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa70f2dbee018b7c</t>
+          <t>https://www.indeed.com/viewjob?jk=743af78e2a52e54b</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Palantir Foundry Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2561,14 +2561,14 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b763786ad2e38b4</t>
+          <t>https://www.indeed.com/viewjob?jk=fa70f2dbee018b7c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,14 +2596,14 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5c47c6ff1b8d763</t>
+          <t>https://www.indeed.com/viewjob?jk=6b763786ad2e38b4</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Palantir Foundry Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1176d370cb1ec66e</t>
+          <t>https://www.indeed.com/viewjob?jk=e5c47c6ff1b8d763</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,14 +2666,14 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7dbdd0593036388</t>
+          <t>https://www.indeed.com/viewjob?jk=1176d370cb1ec66e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Palantir Foundry Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ef6dc42abc1b379</t>
+          <t>https://www.indeed.com/viewjob?jk=f7dbdd0593036388</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,14 +2736,14 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dfe58cb3ddb0d22</t>
+          <t>https://www.indeed.com/viewjob?jk=3ef6dc42abc1b379</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bdd6daf0b2fd71e</t>
+          <t>https://www.indeed.com/viewjob?jk=8dfe58cb3ddb0d22</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,14 +2806,14 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e5c22da5a84813b</t>
+          <t>https://www.indeed.com/viewjob?jk=5bdd6daf0b2fd71e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Palantir Foundry Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=984dc7e3ef8ef833</t>
+          <t>https://www.indeed.com/viewjob?jk=0e5c22da5a84813b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer - ML Infrastructure</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Epsilon Labs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, MLOps, Docker</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5b12d9efc6c6a98</t>
+          <t>https://www.indeed.com/viewjob?jk=984dc7e3ef8ef833</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer-Data Platform &amp; Analytics</t>
+          <t>Software Engineer - ML Infrastructure</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Epsilon Labs</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, MLOps, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b950c881dbe97c6</t>
+          <t>https://www.indeed.com/viewjob?jk=e5b12d9efc6c6a98</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Developer - Information Technology</t>
+          <t>Data Engineer-Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3e76c7cba2c5ef</t>
+          <t>https://www.indeed.com/viewjob?jk=5b950c881dbe97c6</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>State Air Resources Board</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fd3a77f9dc14549</t>
+          <t>https://www.indeed.com/viewjob?jk=5f8755d5755bfc0f</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Salesforce Development Engineer II</t>
+          <t>Senior Developer - Information Technology</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, CI/CD, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2bd0abe4afa5b39</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3e76c7cba2c5ef</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Hightower Advisors</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, Snowflake, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0d0534e87a93a57</t>
+          <t>https://www.indeed.com/viewjob?jk=0fd3a77f9dc14549</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Salesforce Development Engineer II</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Plan A Technologies</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, DataOps, CI/CD, Terraform, Docker, CloudWatch</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d47e70c4d7b465c7</t>
+          <t>https://www.indeed.com/viewjob?jk=b2bd0abe4afa5b39</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Integrations Engineer I</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Kendra Scott</t>
+          <t>Hightower Advisors</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58b78bbfcdcc6779</t>
+          <t>https://www.indeed.com/viewjob?jk=c0d0534e87a93a57</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer - SQL and Snowflake</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Plan A Technologies</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, S3, ECS, RDS, Scala, DataOps, CI/CD, Terraform, Docker, CloudWatch</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c79cad4a6a280f3</t>
+          <t>https://www.indeed.com/viewjob?jk=d47e70c4d7b465c7</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>GenAI Python Systems Engineer – Experienced Associate</t>
+          <t>Senior Integrations Engineer I</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>Kendra Scott</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Terraform, AWS CloudFormation, Docker, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=092180f6fccecac1</t>
+          <t>https://www.indeed.com/viewjob?jk=58b78bbfcdcc6779</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Analytics Engineer, Day Shift, Strategic Analytics</t>
+          <t>Specialist, Data Engineer - SQL and Snowflake</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Adventist HealthCare</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>EMR, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc034fd3ef508e12</t>
+          <t>https://www.indeed.com/viewjob?jk=5c79cad4a6a280f3</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>GenAI Python Systems Engineer – Experienced Associate</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Reach Financial</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, Tableau, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Terraform, AWS CloudFormation, Docker, Python</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62588f4999e63221</t>
+          <t>https://www.indeed.com/viewjob?jk=092180f6fccecac1</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Palantir Foundry</t>
+          <t>Analytics Engineer, Day Shift, Strategic Analytics</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>Adventist HealthCare</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
+          <t>EMR, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d5ca9632878562c</t>
+          <t>https://www.indeed.com/viewjob?jk=fc034fd3ef508e12</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior UX Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GRVTY</t>
+          <t>Reach Financial</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=188385fe594d1176</t>
+          <t>https://www.indeed.com/viewjob?jk=62588f4999e63221</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr. Fullstack Developer</t>
+          <t>Senior Data Engineer - Palantir Foundry</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b803553ffc2f5e53</t>
+          <t>https://www.indeed.com/viewjob?jk=0d5ca9632878562c</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Python Developer Senior</t>
+          <t>Senior UX Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Spark, PySpark, Scala, Dask, Polars, PostgreSQL, Data Modeling, ETL, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1b165e2a50dc910</t>
+          <t>https://www.indeed.com/viewjob?jk=188385fe594d1176</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AI Software Architect</t>
+          <t>Sr. Fullstack Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Park Place Technologies</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Highland Heights, OH, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, MLOps, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5333ce5a9b1f0a9f</t>
+          <t>https://www.indeed.com/viewjob?jk=b803553ffc2f5e53</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>IT Systems Engineer III</t>
+          <t>AI Software Architect</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>Park Place Technologies</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Palm Beach Gardens, FL, US USA</t>
+          <t>Highland Heights, OH, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,17 +3461,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, PostgreSQL, ETL, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, MLOps, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371bf76528aae202</t>
+          <t>https://www.indeed.com/viewjob?jk=5333ce5a9b1f0a9f</t>
         </is>
       </c>
     </row>
@@ -3548,17 +3548,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>IT Systems Engineer III</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palm Beach Gardens, FL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,17 +3566,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, PostgreSQL, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08083d178d541b5c</t>
+          <t>https://www.indeed.com/viewjob?jk=371bf76528aae202</t>
         </is>
       </c>
     </row>
@@ -3618,17 +3618,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AI Engineer — GTM Analytics</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Databricks Lakehouse, ELT, dbt, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f9697dd941d556f</t>
+          <t>https://www.indeed.com/viewjob?jk=08083d178d541b5c</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Python Engineer, Financial Data Platform &amp; Integrations</t>
+          <t>AI Engineer — GTM Analytics</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Cardiff</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, Snowflake, Data Modeling, ETL, CI/CD</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Databricks Lakehouse, ELT, dbt, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44c5ea64ad488307</t>
+          <t>https://www.indeed.com/viewjob?jk=0f9697dd941d556f</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Applied AI Engineer III</t>
+          <t>Python Engineer, Financial Data Platform &amp; Integrations</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Cardiff</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,15 +3706,50 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, Snowflake, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=44c5ea64ad488307</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer III</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c84476dc78d41318</t>
         </is>

--- a/results/job_matches_2026-07-31.xlsx
+++ b/results/job_matches_2026-07-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Technical Specialist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>King, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SQS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba8335e79adaef9</t>
+          <t>https://www.indeed.com/viewjob?jk=2bf07ec2da4c3701</t>
         </is>
       </c>
     </row>
@@ -1553,25 +1553,25 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer III (Agentic AI/Java/AWS/Microservices)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41fb8ee0e0bf2d91</t>
+          <t>https://www.indeed.com/viewjob?jk=e9d72ec9cbbadf7a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Consulting Data Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Glue, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9d72ec9cbbadf7a</t>
+          <t>https://www.indeed.com/viewjob?jk=aff47d92a692d4c3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Consulting Data Architect</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aff47d92a692d4c3</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e3f52aa2a3ab7a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Cloud Engineer Senior</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>Freddie Mac</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Athena, S3, API Gateway, IAM, RDS, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e3f52aa2a3ab7a</t>
+          <t>https://www.indeed.com/viewjob?jk=ca6f5d8776368811</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cloud Engineer Senior</t>
+          <t>Senior Data Transformation Data Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Freddie Mac</t>
+          <t>Patriot Bank, N.A.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, API Gateway, IAM, RDS, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca6f5d8776368811</t>
+          <t>https://www.indeed.com/viewjob?jk=7777dc92cdf89b5a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>NYS ITS Expert Software Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway GUARD Insurance Companies</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Menands, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d44e48661eb7c09</t>
+          <t>https://www.indeed.com/viewjob?jk=3578a6d785ac61e9</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Transformation Data Architect</t>
+          <t>Sr Dir Software - Data Platform Engineer - Minneapolis, MN</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Patriot Bank, N.A.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7777dc92cdf89b5a</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8fa88f7e3fd0c2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NYS ITS Expert Software Architect</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Menands, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3578a6d785ac61e9</t>
+          <t>https://www.indeed.com/viewjob?jk=46bd797613407be6</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr Dir Software - Data Platform Engineer - Minneapolis, MN</t>
+          <t>Software Development Engineer II - Gen AI and Innovation Team</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8fa88f7e3fd0c2</t>
+          <t>https://www.indeed.com/viewjob?jk=93f5da6a90e11da1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - Gen AI and Innovation Team</t>
+          <t>Senior Data Analyst (Hybrid - Madison or Austin)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Snowflake, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93f5da6a90e11da1</t>
+          <t>https://www.indeed.com/viewjob?jk=289d005fb52fdb68</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Analyst (Hybrid - Madison or Austin)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Snowflake, Data Modeling, dbt, Power BI</t>
+          <t>AWS, S3, Azure, Databricks, Blob Storage, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=289d005fb52fdb68</t>
+          <t>https://www.indeed.com/viewjob?jk=70a69ee2362e8f4b</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Blob Storage, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70a69ee2362e8f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=87b420bcd07d16a3</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Site Reliability Engineers</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Careers Inc</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
+          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87b420bcd07d16a3</t>
+          <t>https://www.indeed.com/viewjob?jk=22d91b3a0cb9046d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Site Reliability Engineers</t>
+          <t>Software Engineer III - Python, Databricks and AWS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Careers Inc</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22d91b3a0cb9046d</t>
+          <t>https://www.indeed.com/viewjob?jk=cbfe0afb6a8f866d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python, Databricks and AWS</t>
+          <t>Senior CloudOps Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Domo, Inc.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbfe0afb6a8f866d</t>
+          <t>https://www.indeed.com/viewjob?jk=c47bac900059df12</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior CloudOps Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Domo, Inc.</t>
+          <t>Virta Health</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Google Cloud Platform, BigQuery, Scala, dbt, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c47bac900059df12</t>
+          <t>https://www.indeed.com/viewjob?jk=671761ff02fb6ab9</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cloud SME X2</t>
+          <t>Software Engineer (Angular + .NET, Azure)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>Indiana Donor Network</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Juno Beach, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD</t>
+          <t>RDS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a558c1d3bd32ae5</t>
+          <t>https://www.indeed.com/viewjob?jk=e254843359a11bda</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Software Engineer - Early Career - Landmark</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Virta Health</t>
+          <t>Halliburton</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Google Cloud Platform, BigQuery, Scala, dbt, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=671761ff02fb6ab9</t>
+          <t>https://www.indeed.com/viewjob?jk=2854756df3635191</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer (Angular + .NET, Azure)</t>
+          <t>Sr Associate Engineer, IT Software</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Indiana Donor Network</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e254843359a11bda</t>
+          <t>https://www.indeed.com/viewjob?jk=9f18b9877a4bf7ae</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer - Early Career - Landmark</t>
+          <t>Senior BI Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Halliburton</t>
+          <t>Daisy Brand</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2854756df3635191</t>
+          <t>https://www.indeed.com/viewjob?jk=91b1714cc80b634c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer, IT Software</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f18b9877a4bf7ae</t>
+          <t>https://www.indeed.com/viewjob?jk=bc1820a549077871</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior BI Engineer</t>
+          <t>Backend Engineer _ AI Gateway</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Daisy Brand</t>
+          <t>Linstarsolution corporation</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91b1714cc80b634c</t>
+          <t>https://www.indeed.com/viewjob?jk=40978ef369a5ee61</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>AI Foundational Model Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc1820a549077871</t>
+          <t>https://www.indeed.com/viewjob?jk=376d725617b0f2aa</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Backend Engineer _ AI Gateway</t>
+          <t>Cloud SME X2</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Linstarsolution corporation</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Juno Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,42 +2376,42 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40978ef369a5ee61</t>
+          <t>https://www.indeed.com/viewjob?jk=5a558c1d3bd32ae5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AI Foundational Model Engineer</t>
+          <t>Senior Full-Stack Engineer (Go/Typescript)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Plan A Technologies</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=376d725617b0f2aa</t>
+          <t>https://www.indeed.com/viewjob?jk=73913eba01c47259</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer (Go/Typescript)</t>
+          <t>Senior Software Engineer, Promotions</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Plan A Technologies</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73913eba01c47259</t>
+          <t>https://www.indeed.com/viewjob?jk=b535237436c3096a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Promotions</t>
+          <t>Senior Engineer, Data and AI</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>Cisive</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
+          <t>Azure, Databricks, Spark, Scala, NoSQL, Data Modeling, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b535237436c3096a</t>
+          <t>https://www.indeed.com/viewjob?jk=743af78e2a52e54b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data and AI</t>
+          <t>DevOps / Platform Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Cisive</t>
+          <t>Vivacity Tech PBC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,17 +2516,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Scala, NoSQL, Data Modeling, ETL, ELT, MLOps, MLflow</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=743af78e2a52e54b</t>
+          <t>https://www.indeed.com/viewjob?jk=5d39b7b5a88b4d35</t>
         </is>
       </c>
     </row>
@@ -2988,17 +2988,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Developer - Information Technology</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3e76c7cba2c5ef</t>
+          <t>https://www.indeed.com/viewjob?jk=0fd3a77f9dc14549</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Salesforce Development Engineer II</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fd3a77f9dc14549</t>
+          <t>https://www.indeed.com/viewjob?jk=b2bd0abe4afa5b39</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Salesforce Development Engineer II</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Hightower Advisors</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2bd0abe4afa5b39</t>
+          <t>https://www.indeed.com/viewjob?jk=c0d0534e87a93a57</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Hightower Advisors</t>
+          <t>Plan A Technologies</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, Snowflake, DynamoDB</t>
+          <t>AWS, S3, ECS, RDS, Scala, DataOps, CI/CD, Terraform, Docker, CloudWatch</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0d0534e87a93a57</t>
+          <t>https://www.indeed.com/viewjob?jk=d47e70c4d7b465c7</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Senior Integrations Engineer I</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Plan A Technologies</t>
+          <t>Kendra Scott</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, DataOps, CI/CD, Terraform, Docker, CloudWatch</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d47e70c4d7b465c7</t>
+          <t>https://www.indeed.com/viewjob?jk=58b78bbfcdcc6779</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Integrations Engineer I</t>
+          <t>GenAI Python Systems Engineer – Experienced Associate</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Kendra Scott</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Terraform, AWS CloudFormation, Docker, Python</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58b78bbfcdcc6779</t>
+          <t>https://www.indeed.com/viewjob?jk=092180f6fccecac1</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer - SQL and Snowflake</t>
+          <t>Analytics Engineer, Day Shift, Strategic Analytics</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Adventist HealthCare</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>EMR, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c79cad4a6a280f3</t>
+          <t>https://www.indeed.com/viewjob?jk=fc034fd3ef508e12</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>GenAI Python Systems Engineer – Experienced Associate</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>Reach Financial</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Terraform, AWS CloudFormation, Docker, Python</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=092180f6fccecac1</t>
+          <t>https://www.indeed.com/viewjob?jk=62588f4999e63221</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Analytics Engineer, Day Shift, Strategic Analytics</t>
+          <t>Senior Data Engineer - Palantir Foundry</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Adventist HealthCare</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>EMR, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc034fd3ef508e12</t>
+          <t>https://www.indeed.com/viewjob?jk=0d5ca9632878562c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior UX Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Reach Financial</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, Tableau, CI/CD</t>
+          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62588f4999e63221</t>
+          <t>https://www.indeed.com/viewjob?jk=188385fe594d1176</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Palantir Foundry</t>
+          <t>Sr. Fullstack Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d5ca9632878562c</t>
+          <t>https://www.indeed.com/viewjob?jk=b803553ffc2f5e53</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior UX Software Engineer</t>
+          <t>Senior Software Engineer, Ecommerce Web Applications (US/Canada)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GRVTY</t>
+          <t>CSC Generation</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
+          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=188385fe594d1176</t>
+          <t>https://www.indeed.com/viewjob?jk=a55d577c0fda86f2</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr. Fullstack Developer</t>
+          <t>IT Systems Engineer III</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Palm Beach Gardens, FL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, PostgreSQL, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b803553ffc2f5e53</t>
+          <t>https://www.indeed.com/viewjob?jk=371bf76528aae202</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AI Software Architect</t>
+          <t>Senior Software Engineer (Remote) - Radiology</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Park Place Technologies</t>
+          <t>Washington University in St. Louis</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Highland Heights, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, MLOps, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, RDS, Medallion Architecture, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Terraform, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,19 +3471,19 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5333ce5a9b1f0a9f</t>
+          <t>https://www.indeed.com/viewjob?jk=2e445dc5779186f6</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Ecommerce Web Applications (US/Canada)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CSC Generation</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3496,17 +3496,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a55d577c0fda86f2</t>
+          <t>https://www.indeed.com/viewjob?jk=08083d178d541b5c</t>
         </is>
       </c>
     </row>
@@ -3548,17 +3548,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>IT Systems Engineer III</t>
+          <t>AI Engineer — GTM Analytics</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Palm Beach Gardens, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,29 +3566,29 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, PostgreSQL, ETL, Power BI, CI/CD</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Databricks Lakehouse, ELT, dbt, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371bf76528aae202</t>
+          <t>https://www.indeed.com/viewjob?jk=0f9697dd941d556f</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Remote) - Radiology</t>
+          <t>Python Engineer, Financial Data Platform &amp; Integrations</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Washington University in St. Louis</t>
+          <t>Cardiff</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Terraform, Git, Bitbucket</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, Snowflake, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e445dc5779186f6</t>
+          <t>https://www.indeed.com/viewjob?jk=44c5ea64ad488307</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Applied AI Engineer III</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,120 +3636,15 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=08083d178d541b5c</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>AI Engineer — GTM Analytics</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Databricks Lakehouse, ELT, dbt, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f9697dd941d556f</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Python Engineer, Financial Data Platform &amp; Integrations</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Cardiff</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, Snowflake, Data Modeling, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=44c5ea64ad488307</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer III</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c84476dc78d41318</t>
         </is>

--- a/results/job_matches_2026-07-31.xlsx
+++ b/results/job_matches_2026-07-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Cloud DevOps Engineer</t>
+          <t>senior data engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Michael Baker International</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,42 +1046,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8279b19004b6546d</t>
+          <t>https://www.indeed.com/viewjob?jk=6348f1b22dfd1649</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Technical Specialist</t>
+          <t>Senior Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Michael Baker International</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>King, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SQS, API Gateway, IAM</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bf07ec2da4c3701</t>
+          <t>https://www.indeed.com/viewjob?jk=8279b19004b6546d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer II, Procurement, Real Estate &amp; Facilities Analytics</t>
+          <t>Senior Technical Specialist</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>King, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, RDS, Hadoop, Hive, Spark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SQS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4f8c0cf0c31b9e0</t>
+          <t>https://www.indeed.com/viewjob?jk=2bf07ec2da4c3701</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer III - C# / Java</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,67 +1161,67 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=735136a340f06328</t>
+          <t>https://www.indeed.com/viewjob?jk=dba8335e79adaef9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Business Intelligence Engineer II, Procurement, Real Estate &amp; Facilities Analytics</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Museum of Modern Art</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, Athena, S3, RDS, Hadoop, Hive, Spark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bcc4b2fa6c73536</t>
+          <t>https://www.indeed.com/viewjob?jk=a4f8c0cf0c31b9e0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Software Engineer III - C# / Java</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,19 +1231,19 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebbb3368fcab6386</t>
+          <t>https://www.indeed.com/viewjob?jk=735136a340f06328</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>The Museum of Modern Art</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1252,11 +1252,11 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f01a424e09b95ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=9bcc4b2fa6c73536</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer - Onboarding</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sardine</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, dbt, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eafe0da0cb06f132</t>
+          <t>https://www.indeed.com/viewjob?jk=ebbb3368fcab6386</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Business Data Architect</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Spark Streaming</t>
+          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd28b1da9cfe4d40</t>
+          <t>https://www.indeed.com/viewjob?jk=f01a424e09b95ee6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. SW Engineer</t>
+          <t>Data Engineer - Onboarding</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Sardine</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20a004e42eab6632</t>
+          <t>https://www.indeed.com/viewjob?jk=eafe0da0cb06f132</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Production Data Engineer</t>
+          <t>Sr. SW Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MongoDB, ETL, Jenkins, Maven, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50cc2032a060fc77</t>
+          <t>https://www.indeed.com/viewjob?jk=20a004e42eab6632</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI, AWS DevOps, Java/Python Software Engineer III</t>
+          <t>Production Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MongoDB, ETL, Jenkins, Maven, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65068caf46548141</t>
+          <t>https://www.indeed.com/viewjob?jk=50cc2032a060fc77</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Databricks (No Sponsorship Available)</t>
+          <t>AI, AWS DevOps, Java/Python Software Engineer III</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Heritage Construction + Materials</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f8c3d75cc5a59c9</t>
+          <t>https://www.indeed.com/viewjob?jk=65068caf46548141</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior AI/ML Data Engineer</t>
+          <t>Senior Data Engineer - Databricks (No Sponsorship Available)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Public Storage</t>
+          <t>Heritage Construction + Materials</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, dbt, MLflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7493eab3654bd62</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8c3d75cc5a59c9</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI/ML Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Public Storage</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Kafka, Oracle, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, dbt, MLflow</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5685d1301702faa</t>
+          <t>https://www.indeed.com/viewjob?jk=d7493eab3654bd62</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Kafka, Oracle, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9d72ec9cbbadf7a</t>
+          <t>https://www.indeed.com/viewjob?jk=e5685d1301702faa</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Consulting Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aff47d92a692d4c3</t>
+          <t>https://www.indeed.com/viewjob?jk=e9d72ec9cbbadf7a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Consulting Data Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, Glue, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e3f52aa2a3ab7a</t>
+          <t>https://www.indeed.com/viewjob?jk=aff47d92a692d4c3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cloud Engineer Senior</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Freddie Mac</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, API Gateway, IAM, RDS, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca6f5d8776368811</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e3f52aa2a3ab7a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Transformation Data Architect</t>
+          <t>Cloud Engineer Senior</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Patriot Bank, N.A.</t>
+          <t>Freddie Mac</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Athena, S3, API Gateway, IAM, RDS, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7777dc92cdf89b5a</t>
+          <t>https://www.indeed.com/viewjob?jk=ca6f5d8776368811</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>NYS ITS Expert Software Architect</t>
+          <t>Senior Data Transformation Data Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>Patriot Bank, N.A.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Menands, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3578a6d785ac61e9</t>
+          <t>https://www.indeed.com/viewjob?jk=7777dc92cdf89b5a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr Dir Software - Data Platform Engineer - Minneapolis, MN</t>
+          <t>NYS ITS Expert Software Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Menands, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8fa88f7e3fd0c2</t>
+          <t>https://www.indeed.com/viewjob?jk=3578a6d785ac61e9</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Sr Dir Software - Data Platform Engineer - Minneapolis, MN</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46bd797613407be6</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8fa88f7e3fd0c2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - Gen AI and Innovation Team</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93f5da6a90e11da1</t>
+          <t>https://www.indeed.com/viewjob?jk=46bd797613407be6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Analyst (Hybrid - Madison or Austin)</t>
+          <t>Software Development Engineer II - Gen AI and Innovation Team</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Snowflake, Data Modeling, dbt, Power BI</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=289d005fb52fdb68</t>
+          <t>https://www.indeed.com/viewjob?jk=93f5da6a90e11da1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Data Analyst (Hybrid - Madison or Austin)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Blob Storage, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Snowflake, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70a69ee2362e8f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=289d005fb52fdb68</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
+          <t>AWS, S3, Azure, Databricks, Blob Storage, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87b420bcd07d16a3</t>
+          <t>https://www.indeed.com/viewjob?jk=70a69ee2362e8f4b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Site Reliability Engineers</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Careers Inc</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22d91b3a0cb9046d</t>
+          <t>https://www.indeed.com/viewjob?jk=87b420bcd07d16a3</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python, Databricks and AWS</t>
+          <t>Site Reliability Engineers</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Careers Inc</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse</t>
+          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbfe0afb6a8f866d</t>
+          <t>https://www.indeed.com/viewjob?jk=22d91b3a0cb9046d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior CloudOps Engineer</t>
+          <t>Software Engineer III - Python, Databricks and AWS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Domo, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c47bac900059df12</t>
+          <t>https://www.indeed.com/viewjob?jk=cbfe0afb6a8f866d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Senior CloudOps Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Virta Health</t>
+          <t>Domo, Inc.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Google Cloud Platform, BigQuery, Scala, dbt, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=671761ff02fb6ab9</t>
+          <t>https://www.indeed.com/viewjob?jk=c47bac900059df12</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer (Angular + .NET, Azure)</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Indiana Donor Network</t>
+          <t>Virta Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Google Cloud Platform, BigQuery, Scala, dbt, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e254843359a11bda</t>
+          <t>https://www.indeed.com/viewjob?jk=671761ff02fb6ab9</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer - Early Career - Landmark</t>
+          <t>Software Engineer (Angular + .NET, Azure)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Halliburton</t>
+          <t>Indiana Donor Network</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2854756df3635191</t>
+          <t>https://www.indeed.com/viewjob?jk=e254843359a11bda</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer, IT Software</t>
+          <t>Software Engineer - Early Career - Landmark</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Halliburton</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f18b9877a4bf7ae</t>
+          <t>https://www.indeed.com/viewjob?jk=2854756df3635191</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior BI Engineer</t>
+          <t>Sr Associate Engineer, IT Software</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Daisy Brand</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91b1714cc80b634c</t>
+          <t>https://www.indeed.com/viewjob?jk=9f18b9877a4bf7ae</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior BI Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Daisy Brand</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc1820a549077871</t>
+          <t>https://www.indeed.com/viewjob?jk=91b1714cc80b634c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Backend Engineer _ AI Gateway</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Linstarsolution corporation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40978ef369a5ee61</t>
+          <t>https://www.indeed.com/viewjob?jk=bc1820a549077871</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AI Foundational Model Engineer</t>
+          <t>Backend Engineer _ AI Gateway</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Linstarsolution corporation</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=376d725617b0f2aa</t>
+          <t>https://www.indeed.com/viewjob?jk=40978ef369a5ee61</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cloud SME X2</t>
+          <t>AI Foundational Model Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Juno Beach, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,69 +2376,69 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a558c1d3bd32ae5</t>
+          <t>https://www.indeed.com/viewjob?jk=376d725617b0f2aa</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer (Go/Typescript)</t>
+          <t>Cloud SME X2</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Plan A Technologies</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Juno Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73913eba01c47259</t>
+          <t>https://www.indeed.com/viewjob?jk=5a558c1d3bd32ae5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Promotions</t>
+          <t>Senior Full-Stack Engineer (Go/Typescript)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>Plan A Technologies</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b535237436c3096a</t>
+          <t>https://www.indeed.com/viewjob?jk=73913eba01c47259</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data and AI</t>
+          <t>Senior Software Engineer, Promotions</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Cisive</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Scala, NoSQL, Data Modeling, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=743af78e2a52e54b</t>
+          <t>https://www.indeed.com/viewjob?jk=b535237436c3096a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DevOps / Platform Engineer</t>
+          <t>Senior Engineer, Data and AI</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Vivacity Tech PBC</t>
+          <t>Cisive</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>Azure, Databricks, Spark, Scala, NoSQL, Data Modeling, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d39b7b5a88b4d35</t>
+          <t>https://www.indeed.com/viewjob?jk=743af78e2a52e54b</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>DevOps / Platform Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Vivacity Tech PBC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,24 +2551,24 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa70f2dbee018b7c</t>
+          <t>https://www.indeed.com/viewjob?jk=5d39b7b5a88b4d35</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Palantir Foundry Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2596,14 +2596,14 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b763786ad2e38b4</t>
+          <t>https://www.indeed.com/viewjob?jk=fa70f2dbee018b7c</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5c47c6ff1b8d763</t>
+          <t>https://www.indeed.com/viewjob?jk=6b763786ad2e38b4</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Palantir Foundry Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,14 +2666,14 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1176d370cb1ec66e</t>
+          <t>https://www.indeed.com/viewjob?jk=e5c47c6ff1b8d763</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,14 +2701,14 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7dbdd0593036388</t>
+          <t>https://www.indeed.com/viewjob?jk=1176d370cb1ec66e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Palantir Foundry Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ef6dc42abc1b379</t>
+          <t>https://www.indeed.com/viewjob?jk=f7dbdd0593036388</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,14 +2771,14 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dfe58cb3ddb0d22</t>
+          <t>https://www.indeed.com/viewjob?jk=3ef6dc42abc1b379</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bdd6daf0b2fd71e</t>
+          <t>https://www.indeed.com/viewjob?jk=8dfe58cb3ddb0d22</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,14 +2841,14 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e5c22da5a84813b</t>
+          <t>https://www.indeed.com/viewjob?jk=5bdd6daf0b2fd71e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Palantir Foundry Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=984dc7e3ef8ef833</t>
+          <t>https://www.indeed.com/viewjob?jk=0e5c22da5a84813b</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer - ML Infrastructure</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Epsilon Labs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, MLOps, Docker</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5b12d9efc6c6a98</t>
+          <t>https://www.indeed.com/viewjob?jk=984dc7e3ef8ef833</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer-Data Platform &amp; Analytics</t>
+          <t>Software Engineer - ML Infrastructure</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Epsilon Labs</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, MLOps, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b950c881dbe97c6</t>
+          <t>https://www.indeed.com/viewjob?jk=e5b12d9efc6c6a98</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
+          <t>Data Engineer-Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>State Air Resources Board</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f8755d5755bfc0f</t>
+          <t>https://www.indeed.com/viewjob?jk=5b950c881dbe97c6</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>State Air Resources Board</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fd3a77f9dc14549</t>
+          <t>https://www.indeed.com/viewjob?jk=5f8755d5755bfc0f</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Salesforce Development Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2bd0abe4afa5b39</t>
+          <t>https://www.indeed.com/viewjob?jk=0fd3a77f9dc14549</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Salesforce Development Engineer II</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Hightower Advisors</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, Snowflake, DynamoDB</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0d0534e87a93a57</t>
+          <t>https://www.indeed.com/viewjob?jk=b2bd0abe4afa5b39</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Plan A Technologies</t>
+          <t>Hightower Advisors</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, DataOps, CI/CD, Terraform, Docker, CloudWatch</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,59 +3121,59 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d47e70c4d7b465c7</t>
+          <t>https://www.indeed.com/viewjob?jk=c0d0534e87a93a57</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Integrations Engineer I</t>
+          <t>Data Engineer III-(6264)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Kendra Scott</t>
+          <t>itD Tech</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, NoSQL, Docker, Kubernetes</t>
+          <t>RDS, Hadoop, Hive, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58b78bbfcdcc6779</t>
+          <t>https://www.indeed.com/viewjob?jk=0e5bf4b4d80c8151</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>GenAI Python Systems Engineer – Experienced Associate</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>Plan A Technologies</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Terraform, AWS CloudFormation, Docker, Python</t>
+          <t>AWS, S3, ECS, RDS, Scala, DataOps, CI/CD, Terraform, Docker, CloudWatch</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=092180f6fccecac1</t>
+          <t>https://www.indeed.com/viewjob?jk=d47e70c4d7b465c7</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Analytics Engineer, Day Shift, Strategic Analytics</t>
+          <t>Senior Integrations Engineer I</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Adventist HealthCare</t>
+          <t>Kendra Scott</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>EMR, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc034fd3ef508e12</t>
+          <t>https://www.indeed.com/viewjob?jk=58b78bbfcdcc6779</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>GenAI Python Systems Engineer – Experienced Associate</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Reach Financial</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, Tableau, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Terraform, AWS CloudFormation, Docker, Python</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62588f4999e63221</t>
+          <t>https://www.indeed.com/viewjob?jk=092180f6fccecac1</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Palantir Foundry</t>
+          <t>Analytics Engineer, Day Shift, Strategic Analytics</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>Adventist HealthCare</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
+          <t>EMR, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d5ca9632878562c</t>
+          <t>https://www.indeed.com/viewjob?jk=fc034fd3ef508e12</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior UX Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GRVTY</t>
+          <t>Reach Financial</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=188385fe594d1176</t>
+          <t>https://www.indeed.com/viewjob?jk=62588f4999e63221</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr. Fullstack Developer</t>
+          <t>Senior Data Engineer - Palantir Foundry</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b803553ffc2f5e53</t>
+          <t>https://www.indeed.com/viewjob?jk=0d5ca9632878562c</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Ecommerce Web Applications (US/Canada)</t>
+          <t>Senior UX Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CSC Generation</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a55d577c0fda86f2</t>
+          <t>https://www.indeed.com/viewjob?jk=188385fe594d1176</t>
         </is>
       </c>
     </row>
@@ -3443,17 +3443,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Remote) - Radiology</t>
+          <t>Sr. Fullstack Developer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Washington University in St. Louis</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Terraform, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e445dc5779186f6</t>
+          <t>https://www.indeed.com/viewjob?jk=b803553ffc2f5e53</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Python Developer Senior</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
+          <t>Spark, PySpark, Scala, Dask, Polars, PostgreSQL, Data Modeling, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08083d178d541b5c</t>
+          <t>https://www.indeed.com/viewjob?jk=e1b165e2a50dc910</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer (Remote) - Radiology</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Washington University in St. Louis</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, Oracle, MySQL, NoSQL, ETL, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Medallion Architecture, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Terraform, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec9b8320959ff15</t>
+          <t>https://www.indeed.com/viewjob?jk=2e445dc5779186f6</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>AI Engineer — GTM Analytics</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Databricks Lakehouse, ELT, dbt, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f9697dd941d556f</t>
+          <t>https://www.indeed.com/viewjob?jk=08083d178d541b5c</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Python Engineer, Financial Data Platform &amp; Integrations</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Cardiff</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, Snowflake, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Kafka, Oracle, MySQL, NoSQL, ETL, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44c5ea64ad488307</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec9b8320959ff15</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Applied AI Engineer III</t>
+          <t>AI Engineer — GTM Analytics</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,15 +3636,85 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Databricks Lakehouse, ELT, dbt, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f9697dd941d556f</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Python Engineer, Financial Data Platform &amp; Integrations</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Cardiff</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, Snowflake, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=44c5ea64ad488307</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer III</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c84476dc78d41318</t>
         </is>

--- a/results/job_matches_2026-07-31.xlsx
+++ b/results/job_matches_2026-07-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - AWS</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Great American Insurance Group</t>
+          <t>Visibol</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25</v>
+        <v>26.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, SNS, API Gateway</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, RDS, Azure, Google Cloud Platform, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bf61388569c1188</t>
+          <t>https://www.indeed.com/viewjob?jk=2462e8855b10b292</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III - Databricks</t>
+          <t>Senior Cloud Engineer - AWS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Great American Insurance Group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>25</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, SNS, API Gateway</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3097ac152749d4d</t>
+          <t>https://www.indeed.com/viewjob?jk=5bf61388569c1188</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data</t>
+          <t>Software Engineer III - Databricks</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dutch Bros Coffee</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Hive, Spark, PySpark, Kafka</t>
+          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=033eef2f59a1ddd9</t>
+          <t>https://www.indeed.com/viewjob?jk=e3097ac152749d4d</t>
         </is>
       </c>
     </row>
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06fd616fb4621cbc</t>
+          <t>https://www.indeed.com/viewjob?jk=033eef2f59a1ddd9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer, Data</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Smarty</t>
+          <t>Dutch Bros Coffee</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Orem, UT, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SNS, ECS, IAM, Scala</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Hive, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=232fc1791e50c6b0</t>
+          <t>https://www.indeed.com/viewjob?jk=06fd616fb4621cbc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Smarty</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orem, UT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>IAM, RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Vertex AI, Hadoop, Hive, Spark</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SNS, ECS, IAM, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=751ce7cf6c298548</t>
+          <t>https://www.indeed.com/viewjob?jk=232fc1791e50c6b0</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Applied AI SRE III - PxE GPS</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, Splunk, MLOps, MLflow</t>
+          <t>IAM, RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Vertex AI, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d84df72ea9532c51</t>
+          <t>https://www.indeed.com/viewjob?jk=751ce7cf6c298548</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c8966b4d59c6b1</t>
+          <t>https://www.indeed.com/viewjob?jk=d84df72ea9532c51</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62830a371d1e64c4</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c8966b4d59c6b1</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b49a235e6405f16</t>
+          <t>https://www.indeed.com/viewjob?jk=62830a371d1e64c4</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1135d93688985c7c</t>
+          <t>https://www.indeed.com/viewjob?jk=7b49a235e6405f16</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Applied AI SRE III - PxE GPS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS, ECS</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, Splunk, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3bc1c0882246fa5</t>
+          <t>https://www.indeed.com/viewjob?jk=1135d93688985c7c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DataOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Linstarsolution corporation</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, DataOps, CI/CD</t>
+          <t>AWS, EMR, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS, ECS</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be67238d1b6a44a</t>
+          <t>https://www.indeed.com/viewjob?jk=e3bc1c0882246fa5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>DataOps Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Linstarsolution corporation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Oracle, PostgreSQL</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b44d49984ac43ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=3be67238d1b6a44a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BakerHostetler</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, Medallion Architecture, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e610a35113b8a37</t>
+          <t>https://www.indeed.com/viewjob?jk=b44d49984ac43ef9</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Technical Specialist</t>
+          <t>Business Intelligence Engineer II, Procurement, Real Estate &amp; Facilities Analytics</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>King, NC, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SQS, API Gateway, IAM</t>
+          <t>AWS, Athena, S3, RDS, Hadoop, Hive, Spark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bf07ec2da4c3701</t>
+          <t>https://www.indeed.com/viewjob?jk=a4f8c0cf0c31b9e0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer III - C# / Java</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,67 +1161,67 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba8335e79adaef9</t>
+          <t>https://www.indeed.com/viewjob?jk=735136a340f06328</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer II, Procurement, Real Estate &amp; Facilities Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>The Museum of Modern Art</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, RDS, Hadoop, Hive, Spark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4f8c0cf0c31b9e0</t>
+          <t>https://www.indeed.com/viewjob?jk=9bcc4b2fa6c73536</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer III - C# / Java</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,19 +1231,19 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=735136a340f06328</t>
+          <t>https://www.indeed.com/viewjob?jk=ebbb3368fcab6386</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The Museum of Modern Art</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1252,11 +1252,11 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bcc4b2fa6c73536</t>
+          <t>https://www.indeed.com/viewjob?jk=f01a424e09b95ee6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Data Engineer - Onboarding</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Sardine</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebbb3368fcab6386</t>
+          <t>https://www.indeed.com/viewjob?jk=eafe0da0cb06f132</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Sr. SW Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f01a424e09b95ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=20a004e42eab6632</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer - Onboarding</t>
+          <t>Production Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sardine</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, dbt, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MongoDB, ETL, Jenkins, Maven, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eafe0da0cb06f132</t>
+          <t>https://www.indeed.com/viewjob?jk=50cc2032a060fc77</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. SW Engineer</t>
+          <t>AI, AWS DevOps, Java/Python Software Engineer III</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD, Terraform</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20a004e42eab6632</t>
+          <t>https://www.indeed.com/viewjob?jk=65068caf46548141</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Production Data Engineer</t>
+          <t>Senior Data Engineer - Databricks (No Sponsorship Available)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Heritage Construction + Materials</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MongoDB, ETL, Jenkins, Maven, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50cc2032a060fc77</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8c3d75cc5a59c9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI, AWS DevOps, Java/Python Software Engineer III</t>
+          <t>Senior AI/ML Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Public Storage</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, dbt, MLflow</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65068caf46548141</t>
+          <t>https://www.indeed.com/viewjob?jk=d7493eab3654bd62</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Databricks (No Sponsorship Available)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Heritage Construction + Materials</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Kafka, Oracle, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f8c3d75cc5a59c9</t>
+          <t>https://www.indeed.com/viewjob?jk=e5685d1301702faa</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior AI/ML Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Public Storage</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, dbt, MLflow</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7493eab3654bd62</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e3f52aa2a3ab7a</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Kafka, Oracle, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5685d1301702faa</t>
+          <t>https://www.indeed.com/viewjob?jk=e9d72ec9cbbadf7a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Consulting Data Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Glue, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9d72ec9cbbadf7a</t>
+          <t>https://www.indeed.com/viewjob?jk=aff47d92a692d4c3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Consulting Data Architect</t>
+          <t>NYS ITS Expert Software Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Menands, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aff47d92a692d4c3</t>
+          <t>https://www.indeed.com/viewjob?jk=3578a6d785ac61e9</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e3f52aa2a3ab7a</t>
+          <t>https://www.indeed.com/viewjob?jk=46bd797613407be6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cloud Engineer Senior</t>
+          <t>Software Development Engineer II - Gen AI and Innovation Team</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Freddie Mac</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, API Gateway, IAM, RDS, Kafka, CI/CD, Jenkins</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca6f5d8776368811</t>
+          <t>https://www.indeed.com/viewjob?jk=93f5da6a90e11da1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Transformation Data Architect</t>
+          <t>Sr Dir Software - Data Platform Engineer - Minneapolis, MN</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Patriot Bank, N.A.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7777dc92cdf89b5a</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8fa88f7e3fd0c2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>NYS ITS Expert Software Architect</t>
+          <t>Senior Data Analyst (Hybrid - Madison or Austin)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Menands, NY, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Snowflake, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3578a6d785ac61e9</t>
+          <t>https://www.indeed.com/viewjob?jk=289d005fb52fdb68</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr Dir Software - Data Platform Engineer - Minneapolis, MN</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, S3, Azure, Databricks, Blob Storage, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,67 +1826,67 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8fa88f7e3fd0c2</t>
+          <t>https://www.indeed.com/viewjob?jk=70a69ee2362e8f4b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46bd797613407be6</t>
+          <t>https://www.indeed.com/viewjob?jk=87b420bcd07d16a3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - Gen AI and Innovation Team</t>
+          <t>Site Reliability Engineers</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Careers Inc</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93f5da6a90e11da1</t>
+          <t>https://www.indeed.com/viewjob?jk=22d91b3a0cb9046d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Analyst (Hybrid - Madison or Austin)</t>
+          <t>Software Engineer III - Python, Databricks and AWS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Snowflake, Data Modeling, dbt, Power BI</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=289d005fb52fdb68</t>
+          <t>https://www.indeed.com/viewjob?jk=cbfe0afb6a8f866d</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior CloudOps Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Domo, Inc.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Blob Storage, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70a69ee2362e8f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=c47bac900059df12</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Virta Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
+          <t>AWS, ECS, RDS, Google Cloud Platform, BigQuery, Scala, dbt, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87b420bcd07d16a3</t>
+          <t>https://www.indeed.com/viewjob?jk=671761ff02fb6ab9</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Site Reliability Engineers</t>
+          <t>Software Engineer (Angular + .NET, Azure)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Careers Inc</t>
+          <t>Indiana Donor Network</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22d91b3a0cb9046d</t>
+          <t>https://www.indeed.com/viewjob?jk=e254843359a11bda</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python, Databricks and AWS</t>
+          <t>Software Engineer - Early Career - Landmark</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Halliburton</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbfe0afb6a8f866d</t>
+          <t>https://www.indeed.com/viewjob?jk=2854756df3635191</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior CloudOps Engineer</t>
+          <t>Sr Associate Engineer, IT Software</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Domo, Inc.</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c47bac900059df12</t>
+          <t>https://www.indeed.com/viewjob?jk=9f18b9877a4bf7ae</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Senior BI Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Virta Health</t>
+          <t>Daisy Brand</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Google Cloud Platform, BigQuery, Scala, dbt, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=671761ff02fb6ab9</t>
+          <t>https://www.indeed.com/viewjob?jk=91b1714cc80b634c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer (Angular + .NET, Azure)</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Indiana Donor Network</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e254843359a11bda</t>
+          <t>https://www.indeed.com/viewjob?jk=bc1820a549077871</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer - Early Career - Landmark</t>
+          <t>Backend Engineer _ AI Gateway</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Halliburton</t>
+          <t>Linstarsolution corporation</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2854756df3635191</t>
+          <t>https://www.indeed.com/viewjob?jk=40978ef369a5ee61</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer, IT Software</t>
+          <t>AI Foundational Model Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,102 +2246,102 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f18b9877a4bf7ae</t>
+          <t>https://www.indeed.com/viewjob?jk=376d725617b0f2aa</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior BI Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Daisy Brand</t>
+          <t>Stylitics</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91b1714cc80b634c</t>
+          <t>https://www.indeed.com/viewjob?jk=d143b966366bb7dc</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>DevOps / Platform Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Vivacity Tech PBC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Data Modeling, CI/CD</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc1820a549077871</t>
+          <t>https://www.indeed.com/viewjob?jk=5d39b7b5a88b4d35</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Backend Engineer _ AI Gateway</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Linstarsolution corporation</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40978ef369a5ee61</t>
+          <t>https://www.indeed.com/viewjob?jk=fa70f2dbee018b7c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI Foundational Model Engineer</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,59 +2386,59 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=376d725617b0f2aa</t>
+          <t>https://www.indeed.com/viewjob?jk=6b763786ad2e38b4</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cloud SME X2</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Juno Beach, FL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a558c1d3bd32ae5</t>
+          <t>https://www.indeed.com/viewjob?jk=e5c47c6ff1b8d763</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer (Go/Typescript)</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Plan A Technologies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73913eba01c47259</t>
+          <t>https://www.indeed.com/viewjob?jk=1176d370cb1ec66e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Promotions</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b535237436c3096a</t>
+          <t>https://www.indeed.com/viewjob?jk=f7dbdd0593036388</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data and AI</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Cisive</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Scala, NoSQL, Data Modeling, ETL, ELT, MLOps, MLflow</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=743af78e2a52e54b</t>
+          <t>https://www.indeed.com/viewjob?jk=3ef6dc42abc1b379</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DevOps / Platform Engineer</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Vivacity Tech PBC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,17 +2551,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d39b7b5a88b4d35</t>
+          <t>https://www.indeed.com/viewjob?jk=8dfe58cb3ddb0d22</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,14 +2596,14 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa70f2dbee018b7c</t>
+          <t>https://www.indeed.com/viewjob?jk=5bdd6daf0b2fd71e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Palantir Foundry Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b763786ad2e38b4</t>
+          <t>https://www.indeed.com/viewjob?jk=0e5c22da5a84813b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5c47c6ff1b8d763</t>
+          <t>https://www.indeed.com/viewjob?jk=984dc7e3ef8ef833</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Palantir Foundry Data Engineer</t>
+          <t>Software Engineer - ML Infrastructure</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Epsilon Labs</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, MLOps, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1176d370cb1ec66e</t>
+          <t>https://www.indeed.com/viewjob?jk=e5b12d9efc6c6a98</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer-Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7dbdd0593036388</t>
+          <t>https://www.indeed.com/viewjob?jk=5b950c881dbe97c6</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Palantir Foundry Data Engineer</t>
+          <t>Senior Full-Stack Engineer (Go/Typescript)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Plan A Technologies</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ef6dc42abc1b379</t>
+          <t>https://www.indeed.com/viewjob?jk=73913eba01c47259</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Palantir Foundry Data Engineer</t>
+          <t>Senior Software Engineer, Promotions</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dfe58cb3ddb0d22</t>
+          <t>https://www.indeed.com/viewjob?jk=b535237436c3096a</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer - Back End / Java, Spring Boot, Kafka</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Strongsville, OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bdd6daf0b2fd71e</t>
+          <t>https://www.indeed.com/viewjob?jk=a03649e9af32154c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e5c22da5a84813b</t>
+          <t>https://www.indeed.com/viewjob?jk=0fd3a77f9dc14549</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Palantir Foundry Data Engineer</t>
+          <t>Salesforce Development Engineer II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=984dc7e3ef8ef833</t>
+          <t>https://www.indeed.com/viewjob?jk=b2bd0abe4afa5b39</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer - ML Infrastructure</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Epsilon Labs</t>
+          <t>Hightower Advisors</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, MLOps, Docker</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5b12d9efc6c6a98</t>
+          <t>https://www.indeed.com/viewjob?jk=c0d0534e87a93a57</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer-Data Platform &amp; Analytics</t>
+          <t>Data Engineer III-(6264)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>itD Tech</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,17 +2971,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Hadoop, Hive, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b950c881dbe97c6</t>
+          <t>https://www.indeed.com/viewjob?jk=0e5bf4b4d80c8151</t>
         </is>
       </c>
     </row>
@@ -3023,25 +3023,25 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>GenAI Python Systems Engineer – Experienced Associate</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Terraform, AWS CloudFormation, Docker, Python</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fd3a77f9dc14549</t>
+          <t>https://www.indeed.com/viewjob?jk=092180f6fccecac1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Salesforce Development Engineer II</t>
+          <t>Analytics Engineer, Day Shift, Strategic Analytics</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Adventist HealthCare</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>EMR, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2bd0abe4afa5b39</t>
+          <t>https://www.indeed.com/viewjob?jk=fc034fd3ef508e12</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Hightower Advisors</t>
+          <t>Reach Financial</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, Snowflake, DynamoDB</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,42 +3121,42 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0d0534e87a93a57</t>
+          <t>https://www.indeed.com/viewjob?jk=62588f4999e63221</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer III-(6264)</t>
+          <t>Senior Data Engineer - Palantir Foundry</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>itD Tech</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Tableau</t>
+          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e5bf4b4d80c8151</t>
+          <t>https://www.indeed.com/viewjob?jk=0d5ca9632878562c</t>
         </is>
       </c>
     </row>
@@ -3233,17 +3233,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>GenAI Python Systems Engineer – Experienced Associate</t>
+          <t>Advanced Systems Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>ConnectWise</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Terraform, AWS CloudFormation, Docker, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=092180f6fccecac1</t>
+          <t>https://www.indeed.com/viewjob?jk=a6fd8dee63599f0d</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Analytics Engineer, Day Shift, Strategic Analytics</t>
+          <t>Senior UX Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Adventist HealthCare</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>EMR, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc034fd3ef508e12</t>
+          <t>https://www.indeed.com/viewjob?jk=188385fe594d1176</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>IT Systems Engineer III</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Reach Financial</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palm Beach Gardens, FL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, Tableau, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, PostgreSQL, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62588f4999e63221</t>
+          <t>https://www.indeed.com/viewjob?jk=371bf76528aae202</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Palantir Foundry</t>
+          <t>Sr. Fullstack Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d5ca9632878562c</t>
+          <t>https://www.indeed.com/viewjob?jk=b803553ffc2f5e53</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior UX Software Engineer</t>
+          <t>Python Developer Senior</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GRVTY</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
+          <t>Spark, PySpark, Scala, Dask, Polars, PostgreSQL, Data Modeling, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=188385fe594d1176</t>
+          <t>https://www.indeed.com/viewjob?jk=e1b165e2a50dc910</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>IT Systems Engineer III</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Palm Beach Gardens, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, PostgreSQL, ETL, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371bf76528aae202</t>
+          <t>https://www.indeed.com/viewjob?jk=08083d178d541b5c</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr. Fullstack Developer</t>
+          <t>Senior Software Engineer (Remote) - Radiology</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Washington University in St. Louis</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Medallion Architecture, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Terraform, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b803553ffc2f5e53</t>
+          <t>https://www.indeed.com/viewjob?jk=2e445dc5779186f6</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Python Developer Senior</t>
+          <t>AI Engineer — GTM Analytics</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Spark, PySpark, Scala, Dask, Polars, PostgreSQL, Data Modeling, ETL, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Databricks Lakehouse, ELT, dbt, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1b165e2a50dc910</t>
+          <t>https://www.indeed.com/viewjob?jk=0f9697dd941d556f</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Remote) - Radiology</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Washington University in St. Louis</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Terraform, Git, Bitbucket</t>
+          <t>AWS, RDS, Kafka, Oracle, MySQL, NoSQL, ETL, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,182 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e445dc5779186f6</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=08083d178d541b5c</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Minnetonka, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Kafka, Oracle, MySQL, NoSQL, ETL, CI/CD, GitHub Actions, Docker</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=0ec9b8320959ff15</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>AI Engineer — GTM Analytics</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Databricks Lakehouse, ELT, dbt, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f9697dd941d556f</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Python Engineer, Financial Data Platform &amp; Integrations</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Cardiff</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, Snowflake, Data Modeling, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=44c5ea64ad488307</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer III</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c84476dc78d41318</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-31.xlsx
+++ b/results/job_matches_2026-07-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,60 +538,60 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer III - Databricks</t>
+          <t>Cloud Data Platform Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Northern Trust Corp.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, Data Factory, Databricks, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3097ac152749d4d</t>
+          <t>https://www.indeed.com/viewjob?jk=c3babca04d3a4353</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data</t>
+          <t>Software Engineer III - Databricks</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dutch Bros Coffee</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Hive, Spark, PySpark, Kafka</t>
+          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=033eef2f59a1ddd9</t>
+          <t>https://www.indeed.com/viewjob?jk=e3097ac152749d4d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data</t>
+          <t>Data Engineer – Baltimore City, MD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dutch Bros Coffee</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Hive, Spark, PySpark, Kafka</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, IAM, RDS, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06fd616fb4621cbc</t>
+          <t>https://www.indeed.com/viewjob?jk=8df281f957b19fe4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer, Data</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Smarty</t>
+          <t>Dutch Bros Coffee</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Orem, UT, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SNS, ECS, IAM, Scala</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Hive, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=232fc1791e50c6b0</t>
+          <t>https://www.indeed.com/viewjob?jk=033eef2f59a1ddd9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer, Data</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Novanta</t>
+          <t>Dutch Bros Coffee</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Oracle, Dimensional Modeling</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Hive, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d84674d8dbd92bd</t>
+          <t>https://www.indeed.com/viewjob?jk=06fd616fb4621cbc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Smarty</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orem, UT, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>IAM, RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Vertex AI, Hadoop, Hive, Spark</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SNS, ECS, IAM, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=751ce7cf6c298548</t>
+          <t>https://www.indeed.com/viewjob?jk=232fc1791e50c6b0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Applied AI SRE III - PxE GPS</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, Splunk, MLOps, MLflow</t>
+          <t>IAM, RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Vertex AI, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d84df72ea9532c51</t>
+          <t>https://www.indeed.com/viewjob?jk=751ce7cf6c298548</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Applied AI SRE III - PxE GPS</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Novanta</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, Splunk, MLOps, MLflow</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Oracle, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c8966b4d59c6b1</t>
+          <t>https://www.indeed.com/viewjob?jk=1d84674d8dbd92bd</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Applied AI SRE III - PxE GPS</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, Splunk, MLOps, MLflow</t>
+          <t>AWS, EMR, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS, ECS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62830a371d1e64c4</t>
+          <t>https://www.indeed.com/viewjob?jk=e3bc1c0882246fa5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Applied AI SRE III - PxE GPS</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, Splunk, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b49a235e6405f16</t>
+          <t>https://www.indeed.com/viewjob?jk=b44d49984ac43ef9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Applied AI SRE III - PxE GPS</t>
+          <t>senior data engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, Splunk, MLOps, MLflow</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1135d93688985c7c</t>
+          <t>https://www.indeed.com/viewjob?jk=6348f1b22dfd1649</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Michael Baker International</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS, ECS</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,67 +951,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3bc1c0882246fa5</t>
+          <t>https://www.indeed.com/viewjob?jk=8279b19004b6546d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DataOps Engineer</t>
+          <t>Business Intelligence Engineer II, Procurement, Real Estate &amp; Facilities Analytics</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Linstarsolution corporation</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, DataOps, CI/CD</t>
+          <t>AWS, Athena, S3, RDS, Hadoop, Hive, Spark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be67238d1b6a44a</t>
+          <t>https://www.indeed.com/viewjob?jk=a4f8c0cf0c31b9e0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16.7</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,54 +1021,54 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b44d49984ac43ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=ebbb3368fcab6386</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>senior data engineer</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6348f1b22dfd1649</t>
+          <t>https://www.indeed.com/viewjob?jk=f01a424e09b95ee6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Cloud DevOps Engineer</t>
+          <t>Data Engineer - Onboarding</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Michael Baker International</t>
+          <t>Sardine</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1077,11 +1077,11 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,49 +1091,49 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8279b19004b6546d</t>
+          <t>https://www.indeed.com/viewjob?jk=eafe0da0cb06f132</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer II, Procurement, Real Estate &amp; Facilities Analytics</t>
+          <t>Production Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, RDS, Hadoop, Hive, Spark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MongoDB, ETL, Jenkins, Maven, Terraform</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4f8c0cf0c31b9e0</t>
+          <t>https://www.indeed.com/viewjob?jk=50cc2032a060fc77</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer III - C# / Java</t>
+          <t>AI, AWS DevOps, Java/Python Software Engineer III</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1143,15 +1143,15 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=735136a340f06328</t>
+          <t>https://www.indeed.com/viewjob?jk=65068caf46548141</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Databricks (No Sponsorship Available)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Museum of Modern Art</t>
+          <t>Heritage Construction + Materials</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bcc4b2fa6c73536</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8c3d75cc5a59c9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Senior AI/ML Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Public Storage</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, dbt, MLflow</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,19 +1231,19 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebbb3368fcab6386</t>
+          <t>https://www.indeed.com/viewjob?jk=d7493eab3654bd62</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1252,11 +1252,11 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Kafka, Oracle, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f01a424e09b95ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=e5685d1301702faa</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer - Onboarding</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sardine</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eafe0da0cb06f132</t>
+          <t>https://www.indeed.com/viewjob?jk=e9d72ec9cbbadf7a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. SW Engineer</t>
+          <t>Consulting Data Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD, Terraform</t>
+          <t>AWS, Glue, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20a004e42eab6632</t>
+          <t>https://www.indeed.com/viewjob?jk=aff47d92a692d4c3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Production Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MongoDB, ETL, Jenkins, Maven, Terraform</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,137 +1371,137 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50cc2032a060fc77</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e3f52aa2a3ab7a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI, AWS DevOps, Java/Python Software Engineer III</t>
+          <t>Senior Associate, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Westborough, MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Scala, Kafka, Snowflake, MongoDB, NoSQL, Data Modeling, Splunk, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65068caf46548141</t>
+          <t>https://www.indeed.com/viewjob?jk=48cb6757f61255ed</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Databricks (No Sponsorship Available)</t>
+          <t>NYS ITS Expert Software Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Heritage Construction + Materials</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Menands, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f8c3d75cc5a59c9</t>
+          <t>https://www.indeed.com/viewjob?jk=3578a6d785ac61e9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior AI/ML Data Engineer</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Public Storage</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, dbt, MLflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7493eab3654bd62</t>
+          <t>https://www.indeed.com/viewjob?jk=46bd797613407be6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Development Engineer II - Gen AI and Innovation Team</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Kafka, Oracle, PostgreSQL, CI/CD</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5685d1301702faa</t>
+          <t>https://www.indeed.com/viewjob?jk=93f5da6a90e11da1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Data Analyst (Hybrid - Madison or Austin)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Snowflake, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e3f52aa2a3ab7a</t>
+          <t>https://www.indeed.com/viewjob?jk=289d005fb52fdb68</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, S3, Azure, Databricks, Blob Storage, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,137 +1581,137 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9d72ec9cbbadf7a</t>
+          <t>https://www.indeed.com/viewjob?jk=70a69ee2362e8f4b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Consulting Data Architect</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>Scigon</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aff47d92a692d4c3</t>
+          <t>https://www.indeed.com/viewjob?jk=49e29b1ab6a71257</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NYS ITS Expert Software Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Menands, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3578a6d785ac61e9</t>
+          <t>https://www.indeed.com/viewjob?jk=87b420bcd07d16a3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Site Reliability Engineers</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Careers Inc</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46bd797613407be6</t>
+          <t>https://www.indeed.com/viewjob?jk=22d91b3a0cb9046d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - Gen AI and Innovation Team</t>
+          <t>Software Engineer III - Python, Databricks and AWS</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93f5da6a90e11da1</t>
+          <t>https://www.indeed.com/viewjob?jk=cbfe0afb6a8f866d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr Dir Software - Data Platform Engineer - Minneapolis, MN</t>
+          <t>Senior CloudOps Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Domo, Inc.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,67 +1756,67 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8fa88f7e3fd0c2</t>
+          <t>https://www.indeed.com/viewjob?jk=c47bac900059df12</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Analyst (Hybrid - Madison or Austin)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Snowflake, Data Modeling, dbt, Power BI</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, Splunk</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=289d005fb52fdb68</t>
+          <t>https://www.indeed.com/viewjob?jk=fecf6d8da4c516a0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Virta Health</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Blob Storage, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, ECS, RDS, Google Cloud Platform, BigQuery, Scala, dbt, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70a69ee2362e8f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=671761ff02fb6ab9</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer (Angular + .NET, Azure)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Indiana Donor Network</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
+          <t>RDS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87b420bcd07d16a3</t>
+          <t>https://www.indeed.com/viewjob?jk=e254843359a11bda</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Site Reliability Engineers</t>
+          <t>Software Engineer - Early Career - Landmark</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Careers Inc</t>
+          <t>Halliburton</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22d91b3a0cb9046d</t>
+          <t>https://www.indeed.com/viewjob?jk=2854756df3635191</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python, Databricks and AWS</t>
+          <t>Sr Associate Engineer, IT Software</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbfe0afb6a8f866d</t>
+          <t>https://www.indeed.com/viewjob?jk=9f18b9877a4bf7ae</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior CloudOps Engineer</t>
+          <t>Senior BI Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Domo, Inc.</t>
+          <t>Daisy Brand</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c47bac900059df12</t>
+          <t>https://www.indeed.com/viewjob?jk=91b1714cc80b634c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Virta Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Google Cloud Platform, BigQuery, Scala, dbt, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=671761ff02fb6ab9</t>
+          <t>https://www.indeed.com/viewjob?jk=bc1820a549077871</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer (Angular + .NET, Azure)</t>
+          <t>Senior Full-Stack Engineer (Go/Typescript)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Indiana Donor Network</t>
+          <t>Plan A Technologies</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e254843359a11bda</t>
+          <t>https://www.indeed.com/viewjob?jk=73913eba01c47259</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer - Early Career - Landmark</t>
+          <t>Senior Software Engineer, Promotions</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Halliburton</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,102 +2071,102 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2854756df3635191</t>
+          <t>https://www.indeed.com/viewjob?jk=b535237436c3096a</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer, IT Software</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Stylitics</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f18b9877a4bf7ae</t>
+          <t>https://www.indeed.com/viewjob?jk=d143b966366bb7dc</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior BI Engineer</t>
+          <t>DevOps / Platform Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Daisy Brand</t>
+          <t>Vivacity Tech PBC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91b1714cc80b634c</t>
+          <t>https://www.indeed.com/viewjob?jk=5d39b7b5a88b4d35</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Data Modeling, CI/CD</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc1820a549077871</t>
+          <t>https://www.indeed.com/viewjob?jk=fa70f2dbee018b7c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Backend Engineer _ AI Gateway</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Linstarsolution corporation</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40978ef369a5ee61</t>
+          <t>https://www.indeed.com/viewjob?jk=6b763786ad2e38b4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI Foundational Model Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=376d725617b0f2aa</t>
+          <t>https://www.indeed.com/viewjob?jk=e5c47c6ff1b8d763</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Stylitics</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d143b966366bb7dc</t>
+          <t>https://www.indeed.com/viewjob?jk=1176d370cb1ec66e</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DevOps / Platform Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Vivacity Tech PBC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,24 +2306,24 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d39b7b5a88b4d35</t>
+          <t>https://www.indeed.com/viewjob?jk=f7dbdd0593036388</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa70f2dbee018b7c</t>
+          <t>https://www.indeed.com/viewjob?jk=3ef6dc42abc1b379</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b763786ad2e38b4</t>
+          <t>https://www.indeed.com/viewjob?jk=8dfe58cb3ddb0d22</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,14 +2421,14 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5c47c6ff1b8d763</t>
+          <t>https://www.indeed.com/viewjob?jk=5bdd6daf0b2fd71e</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Palantir Foundry Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2456,14 +2456,14 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1176d370cb1ec66e</t>
+          <t>https://www.indeed.com/viewjob?jk=0e5c22da5a84813b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7dbdd0593036388</t>
+          <t>https://www.indeed.com/viewjob?jk=984dc7e3ef8ef833</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Palantir Foundry Data Engineer</t>
+          <t>Software Engineer - ML Infrastructure</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Epsilon Labs</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, MLOps, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ef6dc42abc1b379</t>
+          <t>https://www.indeed.com/viewjob?jk=e5b12d9efc6c6a98</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Palantir Foundry Data Engineer</t>
+          <t>Senior Software Engineer - Back End / Java, Spring Boot, Kafka</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Strongsville, OH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dfe58cb3ddb0d22</t>
+          <t>https://www.indeed.com/viewjob?jk=a03649e9af32154c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bdd6daf0b2fd71e</t>
+          <t>https://www.indeed.com/viewjob?jk=0fd3a77f9dc14549</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Salesforce Development Engineer II</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e5c22da5a84813b</t>
+          <t>https://www.indeed.com/viewjob?jk=b2bd0abe4afa5b39</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Palantir Foundry Data Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Hightower Advisors</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=984dc7e3ef8ef833</t>
+          <t>https://www.indeed.com/viewjob?jk=c0d0534e87a93a57</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer - ML Infrastructure</t>
+          <t>Data Engineer III-(6264)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Epsilon Labs</t>
+          <t>itD Tech</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, MLOps, Docker</t>
+          <t>RDS, Hadoop, Hive, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5b12d9efc6c6a98</t>
+          <t>https://www.indeed.com/viewjob?jk=0e5bf4b4d80c8151</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer-Data Platform &amp; Analytics</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>State Air Resources Board</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,24 +2726,24 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b950c881dbe97c6</t>
+          <t>https://www.indeed.com/viewjob?jk=5f8755d5755bfc0f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer (Go/Typescript)</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2757,11 +2757,11 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, S3, ECS, RDS, Scala, DataOps, CI/CD, Terraform, Docker, CloudWatch</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73913eba01c47259</t>
+          <t>https://www.indeed.com/viewjob?jk=d47e70c4d7b465c7</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Promotions</t>
+          <t>Senior Integrations Engineer I</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>Kendra Scott</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b535237436c3096a</t>
+          <t>https://www.indeed.com/viewjob?jk=58b78bbfcdcc6779</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Back End / Java, Spring Boot, Kafka</t>
+          <t>Data Transformation Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Confie</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Strongsville, OH, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Airflow, Python</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a03649e9af32154c</t>
+          <t>https://www.indeed.com/viewjob?jk=049826f47ea60f4d</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>GenAI Python Systems Engineer – Experienced Associate</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Terraform, AWS CloudFormation, Docker, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fd3a77f9dc14549</t>
+          <t>https://www.indeed.com/viewjob?jk=092180f6fccecac1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Salesforce Development Engineer II</t>
+          <t>Analytics Engineer, Day Shift, Strategic Analytics</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Adventist HealthCare</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>EMR, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2bd0abe4afa5b39</t>
+          <t>https://www.indeed.com/viewjob?jk=fc034fd3ef508e12</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Hightower Advisors</t>
+          <t>Reach Financial</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, Snowflake, DynamoDB</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,67 +2946,67 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0d0534e87a93a57</t>
+          <t>https://www.indeed.com/viewjob?jk=62588f4999e63221</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer III-(6264)</t>
+          <t>Senior Data Engineer - Palantir Foundry</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>itD Tech</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Tableau</t>
+          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e5bf4b4d80c8151</t>
+          <t>https://www.indeed.com/viewjob?jk=0d5ca9632878562c</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
+          <t>Advanced Systems Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>State Air Resources Board</t>
+          <t>ConnectWise</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f8755d5755bfc0f</t>
+          <t>https://www.indeed.com/viewjob?jk=a6fd8dee63599f0d</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>GenAI Python Systems Engineer – Experienced Associate</t>
+          <t>Senior UX Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Terraform, AWS CloudFormation, Docker, Python</t>
+          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=092180f6fccecac1</t>
+          <t>https://www.indeed.com/viewjob?jk=188385fe594d1176</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Analytics Engineer, Day Shift, Strategic Analytics</t>
+          <t>Sr. Fullstack Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Adventist HealthCare</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>EMR, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,19 +3086,19 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc034fd3ef508e12</t>
+          <t>https://www.indeed.com/viewjob?jk=b803553ffc2f5e53</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Reach Financial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62588f4999e63221</t>
+          <t>https://www.indeed.com/viewjob?jk=08083d178d541b5c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Palantir Foundry</t>
+          <t>IT Systems Engineer III</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palm Beach Gardens, FL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, PostgreSQL, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d5ca9632878562c</t>
+          <t>https://www.indeed.com/viewjob?jk=371bf76528aae202</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Plan A Technologies</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, DataOps, CI/CD, Terraform, Docker, CloudWatch</t>
+          <t>AWS, RDS, Kafka, Oracle, MySQL, NoSQL, ETL, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d47e70c4d7b465c7</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec9b8320959ff15</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Integrations Engineer I</t>
+          <t>AI Engineer — GTM Analytics</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Kendra Scott</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, NoSQL, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Databricks Lakehouse, ELT, dbt, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,322 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58b78bbfcdcc6779</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Advanced Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>ConnectWise</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a6fd8dee63599f0d</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Senior UX Software Engineer</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>GRVTY</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Cambridge, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=188385fe594d1176</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>IT Systems Engineer III</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Delan Associates, Inc</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Palm Beach Gardens, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, PostgreSQL, ETL, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=371bf76528aae202</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Sr. Fullstack Developer</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>ExxonMobil</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Spring, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b803553ffc2f5e53</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Python Developer Senior</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Technology Ventures</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Spark, PySpark, Scala, Dask, Polars, PostgreSQL, Data Modeling, ETL, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e1b165e2a50dc910</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=08083d178d541b5c</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Remote) - Radiology</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Washington University in St. Louis</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Medallion Architecture, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Terraform, Git, Bitbucket</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e445dc5779186f6</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>AI Engineer — GTM Analytics</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Databricks Lakehouse, ELT, dbt, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=0f9697dd941d556f</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Minnetonka, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Kafka, Oracle, MySQL, NoSQL, ETL, CI/CD, GitHub Actions, Docker</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec9b8320959ff15</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-31.xlsx
+++ b/results/job_matches_2026-07-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -718,12 +718,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Smarty</t>
+          <t>Masco</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Orem, UT, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SNS, ECS, IAM, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=232fc1791e50c6b0</t>
+          <t>https://www.indeed.com/viewjob?jk=3d37b8249fccee88</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>Databricks Senior Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,17 +766,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IAM, RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Vertex AI, Hadoop, Hive, Spark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, BigQuery, Hadoop</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=751ce7cf6c298548</t>
+          <t>https://www.indeed.com/viewjob?jk=14e6d9e0e8ac190f</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Platform &amp; Database Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS, ECS</t>
+          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3bc1c0882246fa5</t>
+          <t>https://www.indeed.com/viewjob?jk=28b754997a6cb19c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Oracle, PostgreSQL</t>
+          <t>AWS, EMR, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS, ECS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,59 +881,59 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b44d49984ac43ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=e3bc1c0882246fa5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>senior data engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6348f1b22dfd1649</t>
+          <t>https://www.indeed.com/viewjob?jk=b44d49984ac43ef9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Cloud DevOps Engineer</t>
+          <t>senior data engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Michael Baker International</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,87 +941,87 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8279b19004b6546d</t>
+          <t>https://www.indeed.com/viewjob?jk=6348f1b22dfd1649</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer II, Procurement, Real Estate &amp; Facilities Analytics</t>
+          <t>Senior Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Michael Baker International</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, RDS, Hadoop, Hive, Spark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4f8c0cf0c31b9e0</t>
+          <t>https://www.indeed.com/viewjob?jk=8279b19004b6546d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Business Intelligence Engineer II, Procurement, Real Estate &amp; Facilities Analytics</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
+          <t>AWS, Athena, S3, RDS, Hadoop, Hive, Spark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebbb3368fcab6386</t>
+          <t>https://www.indeed.com/viewjob?jk=a4f8c0cf0c31b9e0</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f01a424e09b95ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=ebbb3368fcab6386</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer - Onboarding</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sardine</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, dbt, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eafe0da0cb06f132</t>
+          <t>https://www.indeed.com/viewjob?jk=f01a424e09b95ee6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Production Data Engineer</t>
+          <t>Data Engineer - Onboarding</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Sardine</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MongoDB, ETL, Jenkins, Maven, Terraform</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50cc2032a060fc77</t>
+          <t>https://www.indeed.com/viewjob?jk=eafe0da0cb06f132</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI, AWS DevOps, Java/Python Software Engineer III</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Delta Faucet Company</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65068caf46548141</t>
+          <t>https://www.indeed.com/viewjob?jk=c2a88b7f58cf63d9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Databricks (No Sponsorship Available)</t>
+          <t>Production Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Heritage Construction + Materials</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MongoDB, ETL, Jenkins, Maven, Terraform</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f8c3d75cc5a59c9</t>
+          <t>https://www.indeed.com/viewjob?jk=50cc2032a060fc77</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior AI/ML Data Engineer</t>
+          <t>AI, AWS DevOps, Java/Python Software Engineer III</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Public Storage</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, dbt, MLflow</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7493eab3654bd62</t>
+          <t>https://www.indeed.com/viewjob?jk=65068caf46548141</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer - Databricks (No Sponsorship Available)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Heritage Construction + Materials</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Kafka, Oracle, PostgreSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5685d1301702faa</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8c3d75cc5a59c9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Kafka, Oracle, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9d72ec9cbbadf7a</t>
+          <t>https://www.indeed.com/viewjob?jk=e5685d1301702faa</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Consulting Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aff47d92a692d4c3</t>
+          <t>https://www.indeed.com/viewjob?jk=e9d72ec9cbbadf7a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Consulting Data Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, Glue, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e3f52aa2a3ab7a</t>
+          <t>https://www.indeed.com/viewjob?jk=aff47d92a692d4c3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Associate, Full-Stack Engineer</t>
+          <t>Sr. Data Engineer- Animal Health Nutrition</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Westborough, MA, US USA</t>
+          <t>Wayzata, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Snowflake, MongoDB, NoSQL, Data Modeling, Splunk, CI/CD, Docker</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48cb6757f61255ed</t>
+          <t>https://www.indeed.com/viewjob?jk=ce5e17069dfe6b5e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>NYS ITS Expert Software Architect</t>
+          <t>Sr. Data Engineer- Animal Health Nutrition</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Menands, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3578a6d785ac61e9</t>
+          <t>https://www.indeed.com/viewjob?jk=1c63dce15e809fa4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46bd797613407be6</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e3f52aa2a3ab7a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - Gen AI and Innovation Team</t>
+          <t>Senior Software Architect, Audience Lifecycle</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>NPR</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, Spark, Scala, Snowflake, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93f5da6a90e11da1</t>
+          <t>https://www.indeed.com/viewjob?jk=9334f09070428459</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Analyst (Hybrid - Madison or Austin)</t>
+          <t>NYS ITS Expert Software Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Menands, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Snowflake, Data Modeling, dbt, Power BI</t>
+          <t>RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=289d005fb52fdb68</t>
+          <t>https://www.indeed.com/viewjob?jk=3578a6d785ac61e9</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Associate, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Westborough, MA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,77 +1571,77 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Blob Storage, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Scala, Kafka, Snowflake, MongoDB, NoSQL, Data Modeling, Splunk, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70a69ee2362e8f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=48cb6757f61255ed</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Analyst (Hybrid - Madison or Austin)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Scigon</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Snowflake, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49e29b1ab6a71257</t>
+          <t>https://www.indeed.com/viewjob?jk=289d005fb52fdb68</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
+          <t>AWS, S3, Azure, Databricks, Blob Storage, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,59 +1651,59 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87b420bcd07d16a3</t>
+          <t>https://www.indeed.com/viewjob?jk=70a69ee2362e8f4b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Site Reliability Engineers</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Careers Inc</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22d91b3a0cb9046d</t>
+          <t>https://www.indeed.com/viewjob?jk=46bd797613407be6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python, Databricks and AWS</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Scigon</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbfe0afb6a8f866d</t>
+          <t>https://www.indeed.com/viewjob?jk=49e29b1ab6a71257</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior CloudOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Domo, Inc.</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c47bac900059df12</t>
+          <t>https://www.indeed.com/viewjob?jk=87b420bcd07d16a3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Site Reliability Engineers</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Careers Inc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, Splunk</t>
+          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fecf6d8da4c516a0</t>
+          <t>https://www.indeed.com/viewjob?jk=22d91b3a0cb9046d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Software Engineer III - Python, Databricks and AWS</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Virta Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Google Cloud Platform, BigQuery, Scala, dbt, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=671761ff02fb6ab9</t>
+          <t>https://www.indeed.com/viewjob?jk=cbfe0afb6a8f866d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer (Angular + .NET, Azure)</t>
+          <t>Senior CloudOps Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Indiana Donor Network</t>
+          <t>Domo, Inc.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e254843359a11bda</t>
+          <t>https://www.indeed.com/viewjob?jk=c47bac900059df12</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer - Early Career - Landmark</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Halliburton</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, Splunk</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2854756df3635191</t>
+          <t>https://www.indeed.com/viewjob?jk=fecf6d8da4c516a0</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer, IT Software</t>
+          <t>Concentra DevOps Engineer II</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Concentra</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f18b9877a4bf7ae</t>
+          <t>https://www.indeed.com/viewjob?jk=937785ffcf01ce69</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior BI Engineer</t>
+          <t>Software Engineer (Angular + .NET, Azure)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Daisy Brand</t>
+          <t>Indiana Donor Network</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
+          <t>RDS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91b1714cc80b634c</t>
+          <t>https://www.indeed.com/viewjob?jk=e254843359a11bda</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Software Engineer - Early Career - Landmark</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Halliburton</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc1820a549077871</t>
+          <t>https://www.indeed.com/viewjob?jk=2854756df3635191</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer (Go/Typescript)</t>
+          <t>Sr Associate Engineer, IT Software</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Plan A Technologies</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73913eba01c47259</t>
+          <t>https://www.indeed.com/viewjob?jk=9f18b9877a4bf7ae</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Promotions</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
+          <t>AWS, SQS, ECS, RDS, Azure, Kafka, SQL Server, DynamoDB, Data Modeling, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b535237436c3096a</t>
+          <t>https://www.indeed.com/viewjob?jk=f4d13644542e7c9f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Full-Stack Engineer (Go/Typescript)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Stylitics</t>
+          <t>Plan A Technologies</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d143b966366bb7dc</t>
+          <t>https://www.indeed.com/viewjob?jk=73913eba01c47259</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DevOps / Platform Engineer</t>
+          <t>Senior Software Engineer, Promotions</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Vivacity Tech PBC</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d39b7b5a88b4d35</t>
+          <t>https://www.indeed.com/viewjob?jk=b535237436c3096a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Stylitics</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa70f2dbee018b7c</t>
+          <t>https://www.indeed.com/viewjob?jk=d143b966366bb7dc</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Palantir Foundry Data Engineer</t>
+          <t>DevOps / Platform Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Vivacity Tech PBC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,17 +2201,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b763786ad2e38b4</t>
+          <t>https://www.indeed.com/viewjob?jk=5d39b7b5a88b4d35</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5c47c6ff1b8d763</t>
+          <t>https://www.indeed.com/viewjob?jk=fa70f2dbee018b7c</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1176d370cb1ec66e</t>
+          <t>https://www.indeed.com/viewjob?jk=6b763786ad2e38b4</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7dbdd0593036388</t>
+          <t>https://www.indeed.com/viewjob?jk=e5c47c6ff1b8d763</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,14 +2351,14 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ef6dc42abc1b379</t>
+          <t>https://www.indeed.com/viewjob?jk=1176d370cb1ec66e</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Palantir Foundry Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2386,14 +2386,14 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dfe58cb3ddb0d22</t>
+          <t>https://www.indeed.com/viewjob?jk=f7dbdd0593036388</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2421,14 +2421,14 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bdd6daf0b2fd71e</t>
+          <t>https://www.indeed.com/viewjob?jk=3ef6dc42abc1b379</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,14 +2456,14 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e5c22da5a84813b</t>
+          <t>https://www.indeed.com/viewjob?jk=8dfe58cb3ddb0d22</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Palantir Foundry Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=984dc7e3ef8ef833</t>
+          <t>https://www.indeed.com/viewjob?jk=5bdd6daf0b2fd71e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer - ML Infrastructure</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Epsilon Labs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, MLOps, Docker</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5b12d9efc6c6a98</t>
+          <t>https://www.indeed.com/viewjob?jk=0e5c22da5a84813b</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Back End / Java, Spring Boot, Kafka</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Strongsville, OH, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a03649e9af32154c</t>
+          <t>https://www.indeed.com/viewjob?jk=984dc7e3ef8ef833</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer - ML Infrastructure</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Epsilon Labs</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, MLOps, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fd3a77f9dc14549</t>
+          <t>https://www.indeed.com/viewjob?jk=e5b12d9efc6c6a98</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Salesforce Development Engineer II</t>
+          <t>Senior Software Engineer - Back End / Java, Spring Boot, Kafka</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Strongsville, OH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2bd0abe4afa5b39</t>
+          <t>https://www.indeed.com/viewjob?jk=a03649e9af32154c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Hightower Advisors</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, Snowflake, DynamoDB</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, MongoDB, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0d0534e87a93a57</t>
+          <t>https://www.indeed.com/viewjob?jk=74263f4a52c96ca9</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer III-(6264)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>itD Tech</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e5bf4b4d80c8151</t>
+          <t>https://www.indeed.com/viewjob?jk=0fd3a77f9dc14549</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>State Air Resources Board</t>
+          <t>Hightower Advisors</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,69 +2726,69 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f8755d5755bfc0f</t>
+          <t>https://www.indeed.com/viewjob?jk=c0d0534e87a93a57</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Data Engineer III-(6264)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Plan A Technologies</t>
+          <t>itD Tech</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, DataOps, CI/CD, Terraform, Docker, CloudWatch</t>
+          <t>RDS, Hadoop, Hive, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d47e70c4d7b465c7</t>
+          <t>https://www.indeed.com/viewjob?jk=0e5bf4b4d80c8151</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Integrations Engineer I</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Kendra Scott</t>
+          <t>Plan A Technologies</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, S3, ECS, RDS, Scala, DataOps, CI/CD, Terraform, Docker, CloudWatch</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58b78bbfcdcc6779</t>
+          <t>https://www.indeed.com/viewjob?jk=d47e70c4d7b465c7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Transformation Engineer</t>
+          <t>Senior Integrations Engineer I</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Confie</t>
+          <t>Kendra Scott</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Airflow, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=049826f47ea60f4d</t>
+          <t>https://www.indeed.com/viewjob?jk=58b78bbfcdcc6779</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>GenAI Python Systems Engineer – Experienced Associate</t>
+          <t>Data Transformation Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>Confie</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Terraform, AWS CloudFormation, Docker, Python</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Airflow, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=092180f6fccecac1</t>
+          <t>https://www.indeed.com/viewjob?jk=049826f47ea60f4d</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Analytics Engineer, Day Shift, Strategic Analytics</t>
+          <t>GenAI Python Systems Engineer – Experienced Associate</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Adventist HealthCare</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>EMR, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Terraform, AWS CloudFormation, Docker, Python</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc034fd3ef508e12</t>
+          <t>https://www.indeed.com/viewjob?jk=092180f6fccecac1</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Analytics Engineer, Day Shift, Strategic Analytics</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Reach Financial</t>
+          <t>Adventist HealthCare</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, Tableau, CI/CD</t>
+          <t>EMR, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62588f4999e63221</t>
+          <t>https://www.indeed.com/viewjob?jk=fc034fd3ef508e12</t>
         </is>
       </c>
     </row>
@@ -2988,17 +2988,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Advanced Systems Engineer</t>
+          <t>Senior UX Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ConnectWise</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Docker</t>
+          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6fd8dee63599f0d</t>
+          <t>https://www.indeed.com/viewjob?jk=188385fe594d1176</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior UX Software Engineer</t>
+          <t>Sr. Fullstack Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GRVTY</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=188385fe594d1176</t>
+          <t>https://www.indeed.com/viewjob?jk=b803553ffc2f5e53</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Fullstack Developer</t>
+          <t>Advanced Systems Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>ConnectWise</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b803553ffc2f5e53</t>
+          <t>https://www.indeed.com/viewjob?jk=a6fd8dee63599f0d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Engineer — GTM Analytics</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Databricks Lakehouse, ELT, dbt, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08083d178d541b5c</t>
+          <t>https://www.indeed.com/viewjob?jk=0f9697dd941d556f</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>IT Systems Engineer III</t>
+          <t>Python Developer Senior</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Palm Beach Gardens, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,17 +3146,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, PostgreSQL, ETL, Power BI, CI/CD</t>
+          <t>Spark, PySpark, Scala, Dask, Polars, PostgreSQL, Data Modeling, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371bf76528aae202</t>
+          <t>https://www.indeed.com/viewjob?jk=e1b165e2a50dc910</t>
         </is>
       </c>
     </row>
@@ -3198,17 +3198,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AI Engineer — GTM Analytics</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,17 +3216,52 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Databricks Lakehouse, ELT, dbt, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f9697dd941d556f</t>
+          <t>https://www.indeed.com/viewjob?jk=08083d178d541b5c</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>IT Systems Engineer III</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Delan Associates, Inc</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Palm Beach Gardens, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, PostgreSQL, ETL, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=371bf76528aae202</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-31.xlsx
+++ b/results/job_matches_2026-07-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,95 +503,95 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - AWS</t>
+          <t>Cloud Data Platform Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Great American Insurance Group</t>
+          <t>Northern Trust Corp.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>25</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, SNS, API Gateway</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, Data Factory, Databricks, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bf61388569c1188</t>
+          <t>https://www.indeed.com/viewjob?jk=c3babca04d3a4353</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Engineer</t>
+          <t>Software Engineer III - Databricks</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Northern Trust Corp.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, Data Factory, Databricks, Scala</t>
+          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3babca04d3a4353</t>
+          <t>https://www.indeed.com/viewjob?jk=e3097ac152749d4d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer III - Databricks</t>
+          <t>Data Engineer – Baltimore City, MD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, IAM, RDS, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3097ac152749d4d</t>
+          <t>https://www.indeed.com/viewjob?jk=8df281f957b19fe4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer – Baltimore City, MD</t>
+          <t>Senior Engineer, Data</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Creative Information Technology India</t>
+          <t>Dutch Bros Coffee</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, IAM, RDS, Medallion Architecture, Spark</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Hive, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8df281f957b19fe4</t>
+          <t>https://www.indeed.com/viewjob?jk=033eef2f59a1ddd9</t>
         </is>
       </c>
     </row>
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=033eef2f59a1ddd9</t>
+          <t>https://www.indeed.com/viewjob?jk=06fd616fb4621cbc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dutch Bros Coffee</t>
+          <t>Masco</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Hive, Spark, PySpark, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06fd616fb4621cbc</t>
+          <t>https://www.indeed.com/viewjob?jk=3d37b8249fccee88</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Senior Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Masco</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Dimensional Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, BigQuery, Hadoop</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d37b8249fccee88</t>
+          <t>https://www.indeed.com/viewjob?jk=14e6d9e0e8ac190f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Databricks Senior Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>Novanta</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,77 +766,77 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, BigQuery, Hadoop</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Oracle, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e6d9e0e8ac190f</t>
+          <t>https://www.indeed.com/viewjob?jk=1d84674d8dbd92bd</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Platform &amp; Database Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Novanta</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Oracle, Dimensional Modeling</t>
+          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d84674d8dbd92bd</t>
+          <t>https://www.indeed.com/viewjob?jk=28b754997a6cb19c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Databricks Platform &amp; Database Engineer</t>
+          <t>senior data engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,137 +846,137 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28b754997a6cb19c</t>
+          <t>https://www.indeed.com/viewjob?jk=6348f1b22dfd1649</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Business Intelligence Engineer II, Procurement, Real Estate &amp; Facilities Analytics</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS, ECS</t>
+          <t>AWS, Athena, S3, RDS, Hadoop, Hive, Spark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3bc1c0882246fa5</t>
+          <t>https://www.indeed.com/viewjob?jk=a4f8c0cf0c31b9e0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b44d49984ac43ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=d2d4d6b724af8274</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>senior data engineer</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6348f1b22dfd1649</t>
+          <t>https://www.indeed.com/viewjob?jk=ebbb3368fcab6386</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Cloud DevOps Engineer</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Michael Baker International</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8279b19004b6546d</t>
+          <t>https://www.indeed.com/viewjob?jk=f01a424e09b95ee6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer II, Procurement, Real Estate &amp; Facilities Analytics</t>
+          <t>Solutions Architect (GenAI, Python/Data, AWS)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, RDS, Hadoop, Hive, Spark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SQS, ECS, RDS, GCP, Spark, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4f8c0cf0c31b9e0</t>
+          <t>https://www.indeed.com/viewjob?jk=84992a9d853e715d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Solutions Architect (GenAI, Python/Data, AWS)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,77 +1046,77 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
+          <t>AWS, Lambda, S3, SQS, ECS, RDS, GCP, Spark, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebbb3368fcab6386</t>
+          <t>https://www.indeed.com/viewjob?jk=794fcf67de18d24f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>Delta Faucet Company</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f01a424e09b95ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=c2a88b7f58cf63d9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer - Onboarding</t>
+          <t>Production Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sardine</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, dbt, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MongoDB, ETL, Jenkins, Maven, Terraform</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eafe0da0cb06f132</t>
+          <t>https://www.indeed.com/viewjob?jk=50cc2032a060fc77</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI, AWS DevOps, Java/Python Software Engineer III</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Delta Faucet Company</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,42 +1151,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2a88b7f58cf63d9</t>
+          <t>https://www.indeed.com/viewjob?jk=65068caf46548141</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Production Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MongoDB, ETL, Jenkins, Maven, Terraform</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50cc2032a060fc77</t>
+          <t>https://www.indeed.com/viewjob?jk=e9d72ec9cbbadf7a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI, AWS DevOps, Java/Python Software Engineer III</t>
+          <t>Sr. Data Engineer- Animal Health Nutrition</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Wayzata, MN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65068caf46548141</t>
+          <t>https://www.indeed.com/viewjob?jk=ce5e17069dfe6b5e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Databricks (No Sponsorship Available)</t>
+          <t>Sr. Data Engineer- Animal Health Nutrition</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Heritage Construction + Materials</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f8c3d75cc5a59c9</t>
+          <t>https://www.indeed.com/viewjob?jk=1c63dce15e809fa4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Kafka, Oracle, PostgreSQL, CI/CD</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5685d1301702faa</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e3f52aa2a3ab7a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Compass</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9d72ec9cbbadf7a</t>
+          <t>https://www.indeed.com/viewjob?jk=edefefd43be9dc66</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Consulting Data Architect</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>Compass Group</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aff47d92a692d4c3</t>
+          <t>https://www.indeed.com/viewjob?jk=fbf25f49dcaa3bab</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer- Animal Health Nutrition</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Compass</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Wayzata, MN, US USA</t>
+          <t>Madison, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce5e17069dfe6b5e</t>
+          <t>https://www.indeed.com/viewjob?jk=be3d62c77468bade</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer- Animal Health Nutrition</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Compass Group</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c63dce15e809fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=f225032bbf5d84c7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>Compass</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Aventura, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e3f52aa2a3ab7a</t>
+          <t>https://www.indeed.com/viewjob?jk=a1b07860a5889799</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Architect, Audience Lifecycle</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NPR</t>
+          <t>Modus Closing</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, Spark, Scala, Snowflake, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9334f09070428459</t>
+          <t>https://www.indeed.com/viewjob?jk=f3134c6730945c7c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NYS ITS Expert Software Architect</t>
+          <t>Senior Software Architect, Audience Lifecycle</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>NPR</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Menands, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, Spark, Scala, Snowflake, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3578a6d785ac61e9</t>
+          <t>https://www.indeed.com/viewjob?jk=9334f09070428459</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Associate, Full-Stack Engineer</t>
+          <t>NYS ITS Expert Software Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Westborough, MA, US USA</t>
+          <t>Menands, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Snowflake, MongoDB, NoSQL, Data Modeling, Splunk, CI/CD, Docker</t>
+          <t>RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48cb6757f61255ed</t>
+          <t>https://www.indeed.com/viewjob?jk=3578a6d785ac61e9</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Analyst (Hybrid - Madison or Austin)</t>
+          <t>Senior Associate, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Westborough, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Snowflake, Data Modeling, dbt, Power BI</t>
+          <t>RDS, Scala, Kafka, Snowflake, MongoDB, NoSQL, Data Modeling, Splunk, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=289d005fb52fdb68</t>
+          <t>https://www.indeed.com/viewjob?jk=48cb6757f61255ed</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Data Analyst (Hybrid - Madison or Austin)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Blob Storage, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Snowflake, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70a69ee2362e8f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=289d005fb52fdb68</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,42 +1676,42 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, S3, Azure, Databricks, Blob Storage, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46bd797613407be6</t>
+          <t>https://www.indeed.com/viewjob?jk=70a69ee2362e8f4b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Scigon</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49e29b1ab6a71257</t>
+          <t>https://www.indeed.com/viewjob?jk=46bd797613407be6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Scigon</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87b420bcd07d16a3</t>
+          <t>https://www.indeed.com/viewjob?jk=49e29b1ab6a71257</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Site Reliability Engineers</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Careers Inc</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22d91b3a0cb9046d</t>
+          <t>https://www.indeed.com/viewjob?jk=87b420bcd07d16a3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python, Databricks and AWS</t>
+          <t>Site Reliability Engineers</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Careers Inc</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse</t>
+          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbfe0afb6a8f866d</t>
+          <t>https://www.indeed.com/viewjob?jk=22d91b3a0cb9046d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior CloudOps Engineer</t>
+          <t>Software Engineer III - Python, Databricks and AWS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Domo, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c47bac900059df12</t>
+          <t>https://www.indeed.com/viewjob?jk=cbfe0afb6a8f866d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Mitratech</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, Splunk</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Snowflake, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fecf6d8da4c516a0</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fad79af5600169</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Concentra DevOps Engineer II</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Concentra</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Terraform</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, Splunk</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=937785ffcf01ce69</t>
+          <t>https://www.indeed.com/viewjob?jk=fecf6d8da4c516a0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer (Angular + .NET, Azure)</t>
+          <t>Concentra DevOps Engineer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Indiana Donor Network</t>
+          <t>Concentra</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e254843359a11bda</t>
+          <t>https://www.indeed.com/viewjob?jk=937785ffcf01ce69</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer - Early Career - Landmark</t>
+          <t>Software Engineer (Angular + .NET, Azure)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Halliburton</t>
+          <t>Indiana Donor Network</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,59 +2001,59 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2854756df3635191</t>
+          <t>https://www.indeed.com/viewjob?jk=e254843359a11bda</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer, IT Software</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, SQS, ECS, RDS, Azure, Kafka, SQL Server, DynamoDB, Data Modeling, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f18b9877a4bf7ae</t>
+          <t>https://www.indeed.com/viewjob?jk=f4d13644542e7c9f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Full-Stack Engineer (Go/Typescript)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Plan A Technologies</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, SQS, ECS, RDS, Azure, Kafka, SQL Server, DynamoDB, Data Modeling, Terraform</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4d13644542e7c9f</t>
+          <t>https://www.indeed.com/viewjob?jk=73913eba01c47259</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer (Go/Typescript)</t>
+          <t>Senior Software Engineer, Promotions</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Plan A Technologies</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73913eba01c47259</t>
+          <t>https://www.indeed.com/viewjob?jk=b535237436c3096a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Promotions</t>
+          <t>Senior SIEM Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
+          <t>ECS, RDS, Databricks, Cloud Storage, Spark, PySpark, Scala, Kafka, Splunk, DataOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b535237436c3096a</t>
+          <t>https://www.indeed.com/viewjob?jk=41d2133f31f2f069</t>
         </is>
       </c>
     </row>
@@ -2568,17 +2568,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer - ML Infrastructure</t>
+          <t>Senior Software Engineer - Back End / Java, Spring Boot, Kafka</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Epsilon Labs</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Strongsville, OH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, MLOps, Docker</t>
+          <t>RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5b12d9efc6c6a98</t>
+          <t>https://www.indeed.com/viewjob?jk=a03649e9af32154c</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Back End / Java, Spring Boot, Kafka</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Strongsville, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, MongoDB, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a03649e9af32154c</t>
+          <t>https://www.indeed.com/viewjob?jk=74263f4a52c96ca9</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Hightower Advisors</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, MongoDB, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74263f4a52c96ca9</t>
+          <t>https://www.indeed.com/viewjob?jk=c0d0534e87a93a57</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer III-(6265)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>itD Tech</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,104 +2691,104 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Hadoop, Hive, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fd3a77f9dc14549</t>
+          <t>https://www.indeed.com/viewjob?jk=0e5bf4b4d80c8151</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Sr. Data Modeler 4D</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Hightower Advisors</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, Snowflake, DynamoDB</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0d0534e87a93a57</t>
+          <t>https://www.indeed.com/viewjob?jk=58941ecd857176c7</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer III-(6264)</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>itD Tech</t>
+          <t>Plan A Technologies</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Tableau</t>
+          <t>AWS, S3, ECS, RDS, Scala, DataOps, CI/CD, Terraform, Docker, CloudWatch</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e5bf4b4d80c8151</t>
+          <t>https://www.indeed.com/viewjob?jk=d47e70c4d7b465c7</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Senior Integrations Engineer I</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Plan A Technologies</t>
+          <t>Kendra Scott</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, DataOps, CI/CD, Terraform, Docker, CloudWatch</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d47e70c4d7b465c7</t>
+          <t>https://www.indeed.com/viewjob?jk=58b78bbfcdcc6779</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Integrations Engineer I</t>
+          <t>Engineer 2 - Integrated Merchandising</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Kendra Scott</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,17 +2831,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, BigQuery, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58b78bbfcdcc6779</t>
+          <t>https://www.indeed.com/viewjob?jk=14c1f123eec910b1</t>
         </is>
       </c>
     </row>
@@ -2953,17 +2953,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Palantir Foundry</t>
+          <t>Senior UX Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
+          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d5ca9632878562c</t>
+          <t>https://www.indeed.com/viewjob?jk=188385fe594d1176</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior UX Software Engineer</t>
+          <t>Sr. Fullstack Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GRVTY</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=188385fe594d1176</t>
+          <t>https://www.indeed.com/viewjob?jk=b803553ffc2f5e53</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Fullstack Developer</t>
+          <t>Advanced Systems Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>ConnectWise</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b803553ffc2f5e53</t>
+          <t>https://www.indeed.com/viewjob?jk=a6fd8dee63599f0d</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Advanced Systems Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ConnectWise</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Kafka, Oracle, MySQL, NoSQL, ETL, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6fd8dee63599f0d</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec9b8320959ff15</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AI Engineer — GTM Analytics</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Databricks Lakehouse, ELT, dbt, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f9697dd941d556f</t>
+          <t>https://www.indeed.com/viewjob?jk=08083d178d541b5c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Python Developer Senior</t>
+          <t>IT Systems Engineer III</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Palm Beach Gardens, FL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,120 +3146,15 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Spark, PySpark, Scala, Dask, Polars, PostgreSQL, Data Modeling, ETL, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, PostgreSQL, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e1b165e2a50dc910</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Minnetonka, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Kafka, Oracle, MySQL, NoSQL, ETL, CI/CD, GitHub Actions, Docker</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec9b8320959ff15</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=08083d178d541b5c</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>IT Systems Engineer III</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Delan Associates, Inc</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Palm Beach Gardens, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, PostgreSQL, ETL, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=371bf76528aae202</t>
         </is>

--- a/results/job_matches_2026-07-31.xlsx
+++ b/results/job_matches_2026-07-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dutch Bros Coffee</t>
+          <t>Masco</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Hive, Spark, PySpark, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06fd616fb4621cbc</t>
+          <t>https://www.indeed.com/viewjob?jk=3d37b8249fccee88</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Senior Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Masco</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Dimensional Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, BigQuery, Hadoop</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d37b8249fccee88</t>
+          <t>https://www.indeed.com/viewjob?jk=14e6d9e0e8ac190f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Databricks Senior Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>Novanta</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,77 +731,77 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, BigQuery, Hadoop</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Oracle, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e6d9e0e8ac190f</t>
+          <t>https://www.indeed.com/viewjob?jk=1d84674d8dbd92bd</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Platform &amp; Database Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Novanta</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Oracle, Dimensional Modeling</t>
+          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d84674d8dbd92bd</t>
+          <t>https://www.indeed.com/viewjob?jk=28b754997a6cb19c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Databricks Platform &amp; Database Engineer</t>
+          <t>senior data engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,42 +811,42 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28b754997a6cb19c</t>
+          <t>https://www.indeed.com/viewjob?jk=6348f1b22dfd1649</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>senior data engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6348f1b22dfd1649</t>
+          <t>https://www.indeed.com/viewjob?jk=dba8335e79adaef9</t>
         </is>
       </c>
     </row>
@@ -888,25 +888,25 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>Jazwares</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,42 +916,42 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2d4d6b724af8274</t>
+          <t>https://www.indeed.com/viewjob?jk=0bec398ccd65219f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebbb3368fcab6386</t>
+          <t>https://www.indeed.com/viewjob?jk=d2d4d6b724af8274</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f01a424e09b95ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=ebbb3368fcab6386</t>
         </is>
       </c>
     </row>
@@ -1133,25 +1133,25 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI, AWS DevOps, Java/Python Software Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65068caf46548141</t>
+          <t>https://www.indeed.com/viewjob?jk=e9d72ec9cbbadf7a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer- Animal Health Nutrition</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wayzata, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9d72ec9cbbadf7a</t>
+          <t>https://www.indeed.com/viewjob?jk=ce5e17069dfe6b5e</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Wayzata, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce5e17069dfe6b5e</t>
+          <t>https://www.indeed.com/viewjob?jk=1c63dce15e809fa4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer- Animal Health Nutrition</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c63dce15e809fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e3f52aa2a3ab7a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>Compass</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e3f52aa2a3ab7a</t>
+          <t>https://www.indeed.com/viewjob?jk=edefefd43be9dc66</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>Compass Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edefefd43be9dc66</t>
+          <t>https://www.indeed.com/viewjob?jk=fbf25f49dcaa3bab</t>
         </is>
       </c>
     </row>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Compass Group</t>
+          <t>Compass</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Madison, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbf25f49dcaa3bab</t>
+          <t>https://www.indeed.com/viewjob?jk=be3d62c77468bade</t>
         </is>
       </c>
     </row>
@@ -1383,12 +1383,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>Compass Group</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Madison, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3d62c77468bade</t>
+          <t>https://www.indeed.com/viewjob?jk=f225032bbf5d84c7</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Compass Group</t>
+          <t>Compass</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Aventura, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f225032bbf5d84c7</t>
+          <t>https://www.indeed.com/viewjob?jk=a1b07860a5889799</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>Modus Closing</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Aventura, FL, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1b07860a5889799</t>
+          <t>https://www.indeed.com/viewjob?jk=f3134c6730945c7c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Senior Software Architect, Audience Lifecycle</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Modus Closing</t>
+          <t>NPR</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, Spark, Scala, Snowflake, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3134c6730945c7c</t>
+          <t>https://www.indeed.com/viewjob?jk=9334f09070428459</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Architect, Audience Lifecycle</t>
+          <t>Senior Data Analyst (Hybrid - Madison or Austin)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NPR</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, Spark, Scala, Snowflake, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Snowflake, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9334f09070428459</t>
+          <t>https://www.indeed.com/viewjob?jk=289d005fb52fdb68</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NYS ITS Expert Software Architect</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Menands, NY, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, S3, Azure, Databricks, Blob Storage, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3578a6d785ac61e9</t>
+          <t>https://www.indeed.com/viewjob?jk=70a69ee2362e8f4b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Associate, Full-Stack Engineer</t>
+          <t>NYS ITS Expert Software Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Westborough, MA, US USA</t>
+          <t>Menands, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Snowflake, MongoDB, NoSQL, Data Modeling, Splunk, CI/CD, Docker</t>
+          <t>RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48cb6757f61255ed</t>
+          <t>https://www.indeed.com/viewjob?jk=3578a6d785ac61e9</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Analyst (Hybrid - Madison or Austin)</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,104 +1641,104 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Snowflake, Data Modeling, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=289d005fb52fdb68</t>
+          <t>https://www.indeed.com/viewjob?jk=46bd797613407be6</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Scigon</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Blob Storage, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70a69ee2362e8f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=49e29b1ab6a71257</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46bd797613407be6</t>
+          <t>https://www.indeed.com/viewjob?jk=87b420bcd07d16a3</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Site Reliability Engineers</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Scigon</t>
+          <t>Careers Inc</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49e29b1ab6a71257</t>
+          <t>https://www.indeed.com/viewjob?jk=22d91b3a0cb9046d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer III - Python, Databricks and AWS</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87b420bcd07d16a3</t>
+          <t>https://www.indeed.com/viewjob?jk=cbfe0afb6a8f866d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Site Reliability Engineers</t>
+          <t>Web Application Architect 3</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Careers Inc</t>
+          <t>Bloomberg Industry Group</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22d91b3a0cb9046d</t>
+          <t>https://www.indeed.com/viewjob?jk=0251e47fed5cebaa</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python, Databricks and AWS</t>
+          <t>Senior Engineer, MDR</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tokio Marine HCC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,17 +1851,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbfe0afb6a8f866d</t>
+          <t>https://www.indeed.com/viewjob?jk=4b46394a094462f4</t>
         </is>
       </c>
     </row>
@@ -2638,17 +2638,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Data Engineer III-(6265)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Hightower Advisors</t>
+          <t>itD Tech</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,42 +2656,42 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, Snowflake, DynamoDB</t>
+          <t>RDS, Hadoop, Hive, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0d0534e87a93a57</t>
+          <t>https://www.indeed.com/viewjob?jk=0e5bf4b4d80c8151</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer III-(6265)</t>
+          <t>Sr. Data Modeler 4D</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>itD Tech</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Tableau</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e5bf4b4d80c8151</t>
+          <t>https://www.indeed.com/viewjob?jk=58941ecd857176c7</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Data Modeler 4D</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>Plan A Technologies</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Oracle, Data Modeling</t>
+          <t>AWS, S3, ECS, RDS, Scala, DataOps, CI/CD, Terraform, Docker, CloudWatch</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58941ecd857176c7</t>
+          <t>https://www.indeed.com/viewjob?jk=d47e70c4d7b465c7</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Healthcare Analytics Engineer II</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Plan A Technologies</t>
+          <t>agilon health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, DataOps, CI/CD, Terraform, Docker, CloudWatch</t>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d47e70c4d7b465c7</t>
+          <t>https://www.indeed.com/viewjob?jk=552c2268ad654867</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Integrations Engineer I</t>
+          <t>Engineer 2 - Integrated Merchandising</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Kendra Scott</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, BigQuery, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58b78bbfcdcc6779</t>
+          <t>https://www.indeed.com/viewjob?jk=14c1f123eec910b1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Engineer 2 - Integrated Merchandising</t>
+          <t>Data Transformation Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Confie</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Airflow</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Airflow, Python</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14c1f123eec910b1</t>
+          <t>https://www.indeed.com/viewjob?jk=049826f47ea60f4d</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Transformation Engineer</t>
+          <t>GenAI Python Systems Engineer – Experienced Associate</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Confie</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Airflow, Python</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Terraform, AWS CloudFormation, Docker, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=049826f47ea60f4d</t>
+          <t>https://www.indeed.com/viewjob?jk=092180f6fccecac1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>GenAI Python Systems Engineer – Experienced Associate</t>
+          <t>Analytics Engineer, Day Shift, Strategic Analytics</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>Adventist HealthCare</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Terraform, AWS CloudFormation, Docker, Python</t>
+          <t>EMR, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=092180f6fccecac1</t>
+          <t>https://www.indeed.com/viewjob?jk=fc034fd3ef508e12</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Analytics Engineer, Day Shift, Strategic Analytics</t>
+          <t>Senior UX Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Adventist HealthCare</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>EMR, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc034fd3ef508e12</t>
+          <t>https://www.indeed.com/viewjob?jk=188385fe594d1176</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior UX Software Engineer</t>
+          <t>Sr. Fullstack Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GRVTY</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=188385fe594d1176</t>
+          <t>https://www.indeed.com/viewjob?jk=b803553ffc2f5e53</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Fullstack Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Kafka, Oracle, MySQL, NoSQL, ETL, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b803553ffc2f5e53</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec9b8320959ff15</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Advanced Systems Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ConnectWise</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6fd8dee63599f0d</t>
+          <t>https://www.indeed.com/viewjob?jk=08083d178d541b5c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>IT Systems Engineer III</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Palm Beach Gardens, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, Oracle, MySQL, NoSQL, ETL, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, PostgreSQL, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec9b8320959ff15</t>
+          <t>https://www.indeed.com/viewjob?jk=371bf76528aae202</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Advanced Systems Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ConnectWise</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,42 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08083d178d541b5c</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>IT Systems Engineer III</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Delan Associates, Inc</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Palm Beach Gardens, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, PostgreSQL, ETL, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=371bf76528aae202</t>
+          <t>https://www.indeed.com/viewjob?jk=a6fd8dee63599f0d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-31.xlsx
+++ b/results/job_matches_2026-07-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dutch Bros Coffee</t>
+          <t>Masco</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,42 +626,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Hive, Spark, PySpark, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=033eef2f59a1ddd9</t>
+          <t>https://www.indeed.com/viewjob?jk=3d37b8249fccee88</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Senior Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Masco</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Dimensional Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, BigQuery, Hadoop</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d37b8249fccee88</t>
+          <t>https://www.indeed.com/viewjob?jk=14e6d9e0e8ac190f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Databricks Senior Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>Novanta</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, BigQuery, Hadoop</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Oracle, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e6d9e0e8ac190f</t>
+          <t>https://www.indeed.com/viewjob?jk=1d84674d8dbd92bd</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Enterprise / Solution Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Novanta</t>
+          <t>Globant</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Oracle, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, API Gateway, RDS, Azure</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d84674d8dbd92bd</t>
+          <t>https://www.indeed.com/viewjob?jk=7ea47f9494f78051</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Databricks Platform &amp; Database Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Whisker</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, Kinesis, API Gateway, ECS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28b754997a6cb19c</t>
+          <t>https://www.indeed.com/viewjob?jk=9fcc3b31ffee88c1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>senior data engineer</t>
+          <t>Databricks Platform &amp; Database Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,59 +811,59 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6348f1b22dfd1649</t>
+          <t>https://www.indeed.com/viewjob?jk=28b754997a6cb19c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>senior data engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba8335e79adaef9</t>
+          <t>https://www.indeed.com/viewjob?jk=6348f1b22dfd1649</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer II, Procurement, Real Estate &amp; Facilities Analytics</t>
+          <t>Senior Technical Specialist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>King, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, RDS, Hadoop, Hive, Spark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SQS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4f8c0cf0c31b9e0</t>
+          <t>https://www.indeed.com/viewjob?jk=2bf07ec2da4c3701</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jazwares</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,112 +906,112 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bec398ccd65219f</t>
+          <t>https://www.indeed.com/viewjob?jk=dba8335e79adaef9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Business Intelligence Engineer II, Procurement, Real Estate &amp; Facilities Analytics</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
+          <t>AWS, Athena, S3, RDS, Hadoop, Hive, Spark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2d4d6b724af8274</t>
+          <t>https://www.indeed.com/viewjob?jk=a4f8c0cf0c31b9e0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Jazwares</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebbb3368fcab6386</t>
+          <t>https://www.indeed.com/viewjob?jk=0bec398ccd65219f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Solutions Architect (GenAI, Python/Data, AWS)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Provectus</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, RDS, GCP, Spark, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84992a9d853e715d</t>
+          <t>https://www.indeed.com/viewjob?jk=d2d4d6b724af8274</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Solutions Architect (GenAI, Python/Data, AWS)</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Provectus</t>
+          <t>Patriot Software</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, RDS, GCP, Spark, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,172 +1056,172 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=794fcf67de18d24f</t>
+          <t>https://www.indeed.com/viewjob?jk=a476aa196196ba0a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Delta Faucet Company</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2a88b7f58cf63d9</t>
+          <t>https://www.indeed.com/viewjob?jk=ebbb3368fcab6386</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Production Data Engineer</t>
+          <t>Solutions Architect (GenAI, Python/Data, AWS)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MongoDB, ETL, Jenkins, Maven, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, ECS, RDS, GCP, Spark, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50cc2032a060fc77</t>
+          <t>https://www.indeed.com/viewjob?jk=84992a9d853e715d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solutions Architect (GenAI, Python/Data, AWS)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, SQS, ECS, RDS, GCP, Spark, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9d72ec9cbbadf7a</t>
+          <t>https://www.indeed.com/viewjob?jk=794fcf67de18d24f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer- Animal Health Nutrition</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Delta Faucet Company</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Wayzata, MN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce5e17069dfe6b5e</t>
+          <t>https://www.indeed.com/viewjob?jk=c2a88b7f58cf63d9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer- Animal Health Nutrition</t>
+          <t>Production Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MongoDB, ETL, Jenkins, Maven, Terraform</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c63dce15e809fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=50cc2032a060fc77</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, BigQuery, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e3f52aa2a3ab7a</t>
+          <t>https://www.indeed.com/viewjob?jk=424fe3c2f51527c0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edefefd43be9dc66</t>
+          <t>https://www.indeed.com/viewjob?jk=e9d72ec9cbbadf7a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Sr. Data Engineer- Animal Health Nutrition</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Compass Group</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Wayzata, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbf25f49dcaa3bab</t>
+          <t>https://www.indeed.com/viewjob?jk=ce5e17069dfe6b5e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Sr. Data Engineer- Animal Health Nutrition</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Madison, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3d62c77468bade</t>
+          <t>https://www.indeed.com/viewjob?jk=1c63dce15e809fa4</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Compass Group</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,17 +1396,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f225032bbf5d84c7</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e3f52aa2a3ab7a</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Aventura, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1b07860a5889799</t>
+          <t>https://www.indeed.com/viewjob?jk=edefefd43be9dc66</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Modus Closing</t>
+          <t>Compass Group</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3134c6730945c7c</t>
+          <t>https://www.indeed.com/viewjob?jk=fbf25f49dcaa3bab</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Architect, Audience Lifecycle</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NPR</t>
+          <t>Compass</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Madison, NJ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, Spark, Scala, Snowflake, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9334f09070428459</t>
+          <t>https://www.indeed.com/viewjob?jk=be3d62c77468bade</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Analyst (Hybrid - Madison or Austin)</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>Compass Group</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Snowflake, Data Modeling, dbt, Power BI</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=289d005fb52fdb68</t>
+          <t>https://www.indeed.com/viewjob?jk=f225032bbf5d84c7</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Compass</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Aventura, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Blob Storage, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70a69ee2362e8f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=a1b07860a5889799</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NYS ITS Expert Software Architect</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>Modus Closing</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Menands, NY, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3578a6d785ac61e9</t>
+          <t>https://www.indeed.com/viewjob?jk=f3134c6730945c7c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Senior Software Architect, Audience Lifecycle</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NPR</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, Spark, Scala, Snowflake, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,94 +1651,94 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46bd797613407be6</t>
+          <t>https://www.indeed.com/viewjob?jk=9334f09070428459</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>NYS ITS Expert Software Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Scigon</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Menands, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49e29b1ab6a71257</t>
+          <t>https://www.indeed.com/viewjob?jk=3578a6d785ac61e9</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87b420bcd07d16a3</t>
+          <t>https://www.indeed.com/viewjob?jk=46bd797613407be6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Site Reliability Engineers</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Careers Inc</t>
+          <t>Scigon</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22d91b3a0cb9046d</t>
+          <t>https://www.indeed.com/viewjob?jk=49e29b1ab6a71257</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python, Databricks and AWS</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse</t>
+          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbfe0afb6a8f866d</t>
+          <t>https://www.indeed.com/viewjob?jk=87b420bcd07d16a3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Web Application Architect 3</t>
+          <t>Site Reliability Engineers</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Bloomberg Industry Group</t>
+          <t>Careers Inc</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0251e47fed5cebaa</t>
+          <t>https://www.indeed.com/viewjob?jk=22d91b3a0cb9046d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Engineer, MDR</t>
+          <t>Software Engineer III - Python, Databricks and AWS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tokio Marine HCC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b46394a094462f4</t>
+          <t>https://www.indeed.com/viewjob?jk=cbfe0afb6a8f866d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Engineer III - Software</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mitratech</t>
+          <t>PODS</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Snowflake, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fad79af5600169</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec22207fa44dd71</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Engineer, MDR</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tokio Marine HCC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, Splunk</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fecf6d8da4c516a0</t>
+          <t>https://www.indeed.com/viewjob?jk=4b46394a094462f4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Concentra DevOps Engineer II</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Concentra</t>
+          <t>Mitratech</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Terraform</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Snowflake, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=937785ffcf01ce69</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fad79af5600169</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer (Angular + .NET, Azure)</t>
+          <t>Web Application Architect 3</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Indiana Donor Network</t>
+          <t>Bloomberg Industry Group</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,42 +1991,42 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e254843359a11bda</t>
+          <t>https://www.indeed.com/viewjob?jk=0251e47fed5cebaa</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, SQS, ECS, RDS, Azure, Kafka, SQL Server, DynamoDB, Data Modeling, Terraform</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, Splunk</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4d13644542e7c9f</t>
+          <t>https://www.indeed.com/viewjob?jk=fecf6d8da4c516a0</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer (Go/Typescript)</t>
+          <t>Concentra DevOps Engineer II</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Plan A Technologies</t>
+          <t>Concentra</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73913eba01c47259</t>
+          <t>https://www.indeed.com/viewjob?jk=937785ffcf01ce69</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Promotions</t>
+          <t>Software Engineer (Angular + .NET, Azure)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>Indiana Donor Network</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
+          <t>RDS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b535237436c3096a</t>
+          <t>https://www.indeed.com/viewjob?jk=e254843359a11bda</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior SIEM Data Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ECS, RDS, Databricks, Cloud Storage, Spark, PySpark, Scala, Kafka, Splunk, DataOps</t>
+          <t>AWS, SQS, ECS, RDS, Azure, Kafka, SQL Server, DynamoDB, Data Modeling, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41d2133f31f2f069</t>
+          <t>https://www.indeed.com/viewjob?jk=f4d13644542e7c9f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Full-Stack Engineer (Go/Typescript)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Stylitics</t>
+          <t>Plan A Technologies</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d143b966366bb7dc</t>
+          <t>https://www.indeed.com/viewjob?jk=73913eba01c47259</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DevOps / Platform Engineer</t>
+          <t>Senior SIEM Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Vivacity Tech PBC</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>ECS, RDS, Databricks, Cloud Storage, Spark, PySpark, Scala, Kafka, Splunk, DataOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d39b7b5a88b4d35</t>
+          <t>https://www.indeed.com/viewjob?jk=41d2133f31f2f069</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Stylitics</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa70f2dbee018b7c</t>
+          <t>https://www.indeed.com/viewjob?jk=d143b966366bb7dc</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Palantir Foundry Data Engineer</t>
+          <t>DevOps / Platform Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Vivacity Tech PBC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,17 +2271,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b763786ad2e38b4</t>
+          <t>https://www.indeed.com/viewjob?jk=5d39b7b5a88b4d35</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5c47c6ff1b8d763</t>
+          <t>https://www.indeed.com/viewjob?jk=fa70f2dbee018b7c</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1176d370cb1ec66e</t>
+          <t>https://www.indeed.com/viewjob?jk=6b763786ad2e38b4</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7dbdd0593036388</t>
+          <t>https://www.indeed.com/viewjob?jk=e5c47c6ff1b8d763</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,14 +2421,14 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ef6dc42abc1b379</t>
+          <t>https://www.indeed.com/viewjob?jk=1176d370cb1ec66e</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Palantir Foundry Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2456,14 +2456,14 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dfe58cb3ddb0d22</t>
+          <t>https://www.indeed.com/viewjob?jk=f7dbdd0593036388</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2491,14 +2491,14 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bdd6daf0b2fd71e</t>
+          <t>https://www.indeed.com/viewjob?jk=3ef6dc42abc1b379</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,14 +2526,14 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e5c22da5a84813b</t>
+          <t>https://www.indeed.com/viewjob?jk=8dfe58cb3ddb0d22</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Palantir Foundry Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=984dc7e3ef8ef833</t>
+          <t>https://www.indeed.com/viewjob?jk=5bdd6daf0b2fd71e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Back End / Java, Spring Boot, Kafka</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Strongsville, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a03649e9af32154c</t>
+          <t>https://www.indeed.com/viewjob?jk=0e5c22da5a84813b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, MongoDB, Data Modeling, CI/CD, Jenkins</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74263f4a52c96ca9</t>
+          <t>https://www.indeed.com/viewjob?jk=984dc7e3ef8ef833</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer III-(6265)</t>
+          <t>Senior Java Backend Engineer (Remote)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>itD Tech</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Tableau</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,19 +2666,19 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e5bf4b4d80c8151</t>
+          <t>https://www.indeed.com/viewjob?jk=131c54e2c46fac8a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Data Modeler 4D</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2687,11 +2687,11 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Oracle, Data Modeling</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, MongoDB, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,67 +2701,67 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58941ecd857176c7</t>
+          <t>https://www.indeed.com/viewjob?jk=74263f4a52c96ca9</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Senior Software Engineer - Back End / Java, Spring Boot, Kafka</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Plan A Technologies</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Strongsville, OH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, DataOps, CI/CD, Terraform, Docker, CloudWatch</t>
+          <t>RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d47e70c4d7b465c7</t>
+          <t>https://www.indeed.com/viewjob?jk=a03649e9af32154c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Healthcare Analytics Engineer II</t>
+          <t>Data Engineer III-(6265)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>agilon health</t>
+          <t>itD Tech</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Git, Bitbucket</t>
+          <t>RDS, Hadoop, Hive, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=552c2268ad654867</t>
+          <t>https://www.indeed.com/viewjob?jk=0e5bf4b4d80c8151</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Engineer 2 - Integrated Merchandising</t>
+          <t>Sr. Data Modeler 4D</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14c1f123eec910b1</t>
+          <t>https://www.indeed.com/viewjob?jk=58941ecd857176c7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Transformation Engineer</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Confie</t>
+          <t>Plan A Technologies</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Airflow, Python</t>
+          <t>AWS, S3, ECS, RDS, Scala, DataOps, CI/CD, Terraform, Docker, CloudWatch</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=049826f47ea60f4d</t>
+          <t>https://www.indeed.com/viewjob?jk=d47e70c4d7b465c7</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>GenAI Python Systems Engineer – Experienced Associate</t>
+          <t>Senior Data &amp; AI Platform Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>Workiva</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Terraform, AWS CloudFormation, Docker, Python</t>
+          <t>AWS, S3, IAM, RDS, Scala, Snowflake, ELT, dbt, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=092180f6fccecac1</t>
+          <t>https://www.indeed.com/viewjob?jk=094ac7b7f209413b</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Analytics Engineer, Day Shift, Strategic Analytics</t>
+          <t>Healthcare Analytics Engineer II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Adventist HealthCare</t>
+          <t>agilon health</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>EMR, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc034fd3ef508e12</t>
+          <t>https://www.indeed.com/viewjob?jk=552c2268ad654867</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior UX Software Engineer</t>
+          <t>Engineer 2 - Integrated Merchandising</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GRVTY</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
+          <t>AWS, RDS, BigQuery, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=188385fe594d1176</t>
+          <t>https://www.indeed.com/viewjob?jk=14c1f123eec910b1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Fullstack Developer</t>
+          <t>Data Transformation Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Confie</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Airflow, Python</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b803553ffc2f5e53</t>
+          <t>https://www.indeed.com/viewjob?jk=049826f47ea60f4d</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>GenAI Python Systems Engineer – Experienced Associate</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, Oracle, MySQL, NoSQL, ETL, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Terraform, AWS CloudFormation, Docker, Python</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec9b8320959ff15</t>
+          <t>https://www.indeed.com/viewjob?jk=092180f6fccecac1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Analytics Engineer, Day Shift, Strategic Analytics</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Adventist HealthCare</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
+          <t>EMR, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08083d178d541b5c</t>
+          <t>https://www.indeed.com/viewjob?jk=fc034fd3ef508e12</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>IT Systems Engineer III</t>
+          <t>Senior UX Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Palm Beach Gardens, FL, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, PostgreSQL, ETL, Power BI, CI/CD</t>
+          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371bf76528aae202</t>
+          <t>https://www.indeed.com/viewjob?jk=188385fe594d1176</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Advanced Systems Engineer</t>
+          <t>Sr. Fullstack Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ConnectWise</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,15 +3111,155 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b803553ffc2f5e53</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Minnetonka, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Kafka, Oracle, MySQL, NoSQL, ETL, CI/CD, GitHub Actions, Docker</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ec9b8320959ff15</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=08083d178d541b5c</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>IT Systems Engineer III</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Delan Associates, Inc</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Palm Beach Gardens, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, PostgreSQL, ETL, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=371bf76528aae202</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Advanced Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>ConnectWise</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Docker</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a6fd8dee63599f0d</t>
         </is>

--- a/results/job_matches_2026-07-31.xlsx
+++ b/results/job_matches_2026-07-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer III - Databricks</t>
+          <t>Data Engineer – Baltimore City, MD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, IAM, RDS, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3097ac152749d4d</t>
+          <t>https://www.indeed.com/viewjob?jk=8df281f957b19fe4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer – Baltimore City, MD</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Creative Information Technology India</t>
+          <t>Masco</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,34 +591,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, IAM, RDS, Medallion Architecture, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8df281f957b19fe4</t>
+          <t>https://www.indeed.com/viewjob?jk=3d37b8249fccee88</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Masco</t>
+          <t>American Century Investments</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS, RDS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d37b8249fccee88</t>
+          <t>https://www.indeed.com/viewjob?jk=0f0b0aed89dff9f0</t>
         </is>
       </c>
     </row>
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Enterprise / Solution Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Novanta</t>
+          <t>Globant</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Oracle, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, API Gateway, RDS, Azure</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d84674d8dbd92bd</t>
+          <t>https://www.indeed.com/viewjob?jk=7ea47f9494f78051</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Enterprise / Solution Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Globant</t>
+          <t>Whisker</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, API Gateway, RDS, Azure</t>
+          <t>AWS, Kinesis, API Gateway, ECS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea47f9494f78051</t>
+          <t>https://www.indeed.com/viewjob?jk=9fcc3b31ffee88c1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Platform &amp; Database Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Whisker</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, ECS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark</t>
+          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fcc3b31ffee88c1</t>
+          <t>https://www.indeed.com/viewjob?jk=28b754997a6cb19c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Databricks Platform &amp; Database Engineer</t>
+          <t>senior data engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,59 +811,59 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28b754997a6cb19c</t>
+          <t>https://www.indeed.com/viewjob?jk=6348f1b22dfd1649</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>senior data engineer</t>
+          <t>Senior Technical Specialist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>King, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SQS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6348f1b22dfd1649</t>
+          <t>https://www.indeed.com/viewjob?jk=2bf07ec2da4c3701</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Technical Specialist</t>
+          <t>Business Intelligence Engineer II, Procurement, Real Estate &amp; Facilities Analytics</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>King, NC, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SQS, API Gateway, IAM</t>
+          <t>AWS, Athena, S3, RDS, Hadoop, Hive, Spark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bf07ec2da4c3701</t>
+          <t>https://www.indeed.com/viewjob?jk=a4f8c0cf0c31b9e0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Jazwares</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,77 +906,77 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba8335e79adaef9</t>
+          <t>https://www.indeed.com/viewjob?jk=0bec398ccd65219f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer II, Procurement, Real Estate &amp; Facilities Analytics</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, RDS, Hadoop, Hive, Spark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4f8c0cf0c31b9e0</t>
+          <t>https://www.indeed.com/viewjob?jk=d2d4d6b724af8274</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jazwares</t>
+          <t>Patriot Software</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bec398ccd65219f</t>
+          <t>https://www.indeed.com/viewjob?jk=a476aa196196ba0a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2d4d6b724af8274</t>
+          <t>https://www.indeed.com/viewjob?jk=ebbb3368fcab6386</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Solutions Architect (GenAI, Python/Data, AWS)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Patriot Software</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SQS, ECS, RDS, GCP, Spark, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a476aa196196ba0a</t>
+          <t>https://www.indeed.com/viewjob?jk=84992a9d853e715d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Solutions Architect (GenAI, Python/Data, AWS)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
+          <t>AWS, Lambda, S3, SQS, ECS, RDS, GCP, Spark, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebbb3368fcab6386</t>
+          <t>https://www.indeed.com/viewjob?jk=794fcf67de18d24f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Solutions Architect (GenAI, Python/Data, AWS)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Provectus</t>
+          <t>Delta Faucet Company</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, RDS, GCP, Spark, ETL, ELT</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,42 +1126,42 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84992a9d853e715d</t>
+          <t>https://www.indeed.com/viewjob?jk=c2a88b7f58cf63d9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Solutions Architect (GenAI, Python/Data, AWS)</t>
+          <t>Production Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Provectus</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, RDS, GCP, Spark, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MongoDB, ETL, Jenkins, Maven, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=794fcf67de18d24f</t>
+          <t>https://www.indeed.com/viewjob?jk=50cc2032a060fc77</t>
         </is>
       </c>
     </row>
@@ -1173,20 +1173,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Delta Faucet Company</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,59 +1196,59 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2a88b7f58cf63d9</t>
+          <t>https://www.indeed.com/viewjob?jk=7e6f4ed087e5ebb6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Production Data Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MongoDB, ETL, Jenkins, Maven, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, BigQuery, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50cc2032a060fc77</t>
+          <t>https://www.indeed.com/viewjob?jk=424fe3c2f51527c0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Sr. Data Engineer- Animal Health Nutrition</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Wayzata, MN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, BigQuery, Snowflake, PostgreSQL</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424fe3c2f51527c0</t>
+          <t>https://www.indeed.com/viewjob?jk=ce5e17069dfe6b5e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer- Animal Health Nutrition</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9d72ec9cbbadf7a</t>
+          <t>https://www.indeed.com/viewjob?jk=1c63dce15e809fa4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer- Animal Health Nutrition</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Wayzata, MN, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce5e17069dfe6b5e</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e3f52aa2a3ab7a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer- Animal Health Nutrition</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Compass</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c63dce15e809fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=edefefd43be9dc66</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>Compass Group</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,17 +1396,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e3f52aa2a3ab7a</t>
+          <t>https://www.indeed.com/viewjob?jk=fbf25f49dcaa3bab</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Madison, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edefefd43be9dc66</t>
+          <t>https://www.indeed.com/viewjob?jk=be3d62c77468bade</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbf25f49dcaa3bab</t>
+          <t>https://www.indeed.com/viewjob?jk=f225032bbf5d84c7</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Madison, NJ, US USA</t>
+          <t>Aventura, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3d62c77468bade</t>
+          <t>https://www.indeed.com/viewjob?jk=a1b07860a5889799</t>
         </is>
       </c>
     </row>
@@ -1523,12 +1523,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Compass Group</t>
+          <t>Modus Closing</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f225032bbf5d84c7</t>
+          <t>https://www.indeed.com/viewjob?jk=f3134c6730945c7c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Senior Software Architect, Audience Lifecycle</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>NPR</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Aventura, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, Spark, Scala, Snowflake, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1b07860a5889799</t>
+          <t>https://www.indeed.com/viewjob?jk=9334f09070428459</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Modus Closing</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3134c6730945c7c</t>
+          <t>https://www.indeed.com/viewjob?jk=46bd797613407be6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Architect, Audience Lifecycle</t>
+          <t>NYS ITS Expert Software Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NPR</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Menands, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,77 +1641,77 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, Spark, Scala, Snowflake, DynamoDB, NoSQL, CI/CD</t>
+          <t>RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9334f09070428459</t>
+          <t>https://www.indeed.com/viewjob?jk=3578a6d785ac61e9</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NYS ITS Expert Software Architect</t>
+          <t>Sr. Software Engineer - PySpark</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Menands, NY, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, PySpark, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3578a6d785ac61e9</t>
+          <t>https://www.indeed.com/viewjob?jk=932b9e36940a351b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Scigon</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46bd797613407be6</t>
+          <t>https://www.indeed.com/viewjob?jk=49e29b1ab6a71257</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Scigon</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49e29b1ab6a71257</t>
+          <t>https://www.indeed.com/viewjob?jk=87b420bcd07d16a3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Engineer III - Software</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>PODS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87b420bcd07d16a3</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec22207fa44dd71</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Site Reliability Engineers</t>
+          <t>Senior Engineer, MDR</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Careers Inc</t>
+          <t>Tokio Marine HCC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22d91b3a0cb9046d</t>
+          <t>https://www.indeed.com/viewjob?jk=4b46394a094462f4</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python, Databricks and AWS</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Mitratech</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Snowflake, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbfe0afb6a8f866d</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fad79af5600169</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Engineer III - Software</t>
+          <t>Web Application Architect 3</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>Bloomberg Industry Group</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec22207fa44dd71</t>
+          <t>https://www.indeed.com/viewjob?jk=0251e47fed5cebaa</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Engineer, MDR</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tokio Marine HCC</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, Splunk</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b46394a094462f4</t>
+          <t>https://www.indeed.com/viewjob?jk=fecf6d8da4c516a0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Concentra DevOps Engineer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Mitratech</t>
+          <t>Concentra</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Snowflake, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fad79af5600169</t>
+          <t>https://www.indeed.com/viewjob?jk=937785ffcf01ce69</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Web Application Architect 3</t>
+          <t>Software Engineer (Angular + .NET, Azure)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Bloomberg Industry Group</t>
+          <t>Indiana Donor Network</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,42 +1991,42 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, DynamoDB</t>
+          <t>RDS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0251e47fed5cebaa</t>
+          <t>https://www.indeed.com/viewjob?jk=e254843359a11bda</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, Splunk</t>
+          <t>AWS, SQS, ECS, RDS, Azure, Kafka, SQL Server, DynamoDB, Data Modeling, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fecf6d8da4c516a0</t>
+          <t>https://www.indeed.com/viewjob?jk=f4d13644542e7c9f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Concentra DevOps Engineer II</t>
+          <t>Senior Full-Stack Engineer (Go/Typescript)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Concentra</t>
+          <t>Plan A Technologies</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Terraform</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,59 +2071,59 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=937785ffcf01ce69</t>
+          <t>https://www.indeed.com/viewjob?jk=73913eba01c47259</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer (Angular + .NET, Azure)</t>
+          <t>Senior SIEM Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Indiana Donor Network</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>ECS, RDS, Databricks, Cloud Storage, Spark, PySpark, Scala, Kafka, Splunk, DataOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e254843359a11bda</t>
+          <t>https://www.indeed.com/viewjob?jk=41d2133f31f2f069</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Stylitics</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, SQS, ECS, RDS, Azure, Kafka, SQL Server, DynamoDB, Data Modeling, Terraform</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,19 +2141,19 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4d13644542e7c9f</t>
+          <t>https://www.indeed.com/viewjob?jk=d143b966366bb7dc</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer (Go/Typescript)</t>
+          <t>DevOps / Platform Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Plan A Technologies</t>
+          <t>Vivacity Tech PBC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73913eba01c47259</t>
+          <t>https://www.indeed.com/viewjob?jk=5d39b7b5a88b4d35</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior SIEM Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ECS, RDS, Databricks, Cloud Storage, Spark, PySpark, Scala, Kafka, Splunk, DataOps</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41d2133f31f2f069</t>
+          <t>https://www.indeed.com/viewjob?jk=fa70f2dbee018b7c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Stylitics</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d143b966366bb7dc</t>
+          <t>https://www.indeed.com/viewjob?jk=6b763786ad2e38b4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DevOps / Platform Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Vivacity Tech PBC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,24 +2271,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d39b7b5a88b4d35</t>
+          <t>https://www.indeed.com/viewjob?jk=e5c47c6ff1b8d763</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,14 +2316,14 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa70f2dbee018b7c</t>
+          <t>https://www.indeed.com/viewjob?jk=1176d370cb1ec66e</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Palantir Foundry Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,14 +2351,14 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b763786ad2e38b4</t>
+          <t>https://www.indeed.com/viewjob?jk=f7dbdd0593036388</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Palantir Foundry Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5c47c6ff1b8d763</t>
+          <t>https://www.indeed.com/viewjob?jk=3ef6dc42abc1b379</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1176d370cb1ec66e</t>
+          <t>https://www.indeed.com/viewjob?jk=8dfe58cb3ddb0d22</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,14 +2456,14 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7dbdd0593036388</t>
+          <t>https://www.indeed.com/viewjob?jk=5bdd6daf0b2fd71e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Palantir Foundry Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ef6dc42abc1b379</t>
+          <t>https://www.indeed.com/viewjob?jk=0e5c22da5a84813b</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dfe58cb3ddb0d22</t>
+          <t>https://www.indeed.com/viewjob?jk=984dc7e3ef8ef833</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Java Backend Engineer (Remote)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bdd6daf0b2fd71e</t>
+          <t>https://www.indeed.com/viewjob?jk=131c54e2c46fac8a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer - Back End / Java, Spring Boot, Kafka</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Strongsville, OH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e5c22da5a84813b</t>
+          <t>https://www.indeed.com/viewjob?jk=a03649e9af32154c</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Palantir Foundry Data Engineer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, MongoDB, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=984dc7e3ef8ef833</t>
+          <t>https://www.indeed.com/viewjob?jk=74263f4a52c96ca9</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer (Remote)</t>
+          <t>Data Engineer III-(6265)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>itD Tech</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>RDS, Hadoop, Hive, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,19 +2666,19 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=131c54e2c46fac8a</t>
+          <t>https://www.indeed.com/viewjob?jk=0e5bf4b4d80c8151</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Sr. Data Modeler 4D</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2687,11 +2687,11 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, MongoDB, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,67 +2701,67 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74263f4a52c96ca9</t>
+          <t>https://www.indeed.com/viewjob?jk=58941ecd857176c7</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Back End / Java, Spring Boot, Kafka</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Plan A Technologies</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Strongsville, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, ECS, RDS, Scala, DataOps, CI/CD, Terraform, Docker, CloudWatch</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a03649e9af32154c</t>
+          <t>https://www.indeed.com/viewjob?jk=d47e70c4d7b465c7</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer III-(6265)</t>
+          <t>IT Engineer - Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>itD Tech</t>
+          <t>Lead Bank</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Tableau</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e5bf4b4d80c8151</t>
+          <t>https://www.indeed.com/viewjob?jk=8ccc9d2a5b9ebc8e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. Data Modeler 4D</t>
+          <t>Senior Data &amp; AI Platform Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>Workiva</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Oracle, Data Modeling</t>
+          <t>AWS, S3, IAM, RDS, Scala, Snowflake, ELT, dbt, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58941ecd857176c7</t>
+          <t>https://www.indeed.com/viewjob?jk=094ac7b7f209413b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Healthcare Analytics Engineer II</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Plan A Technologies</t>
+          <t>agilon health</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, DataOps, CI/CD, Terraform, Docker, CloudWatch</t>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d47e70c4d7b465c7</t>
+          <t>https://www.indeed.com/viewjob?jk=552c2268ad654867</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Platform Engineer</t>
+          <t>Engineer 2 - Integrated Merchandising</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Workiva</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Snowflake, ELT, dbt, Tableau, Airflow</t>
+          <t>AWS, RDS, BigQuery, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=094ac7b7f209413b</t>
+          <t>https://www.indeed.com/viewjob?jk=14c1f123eec910b1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Healthcare Analytics Engineer II</t>
+          <t>Data Transformation Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>agilon health</t>
+          <t>Confie</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Git, Bitbucket</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Airflow, Python</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=552c2268ad654867</t>
+          <t>https://www.indeed.com/viewjob?jk=049826f47ea60f4d</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Engineer 2 - Integrated Merchandising</t>
+          <t>GenAI Python Systems Engineer – Experienced Associate</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Terraform, AWS CloudFormation, Docker, Python</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14c1f123eec910b1</t>
+          <t>https://www.indeed.com/viewjob?jk=092180f6fccecac1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Transformation Engineer</t>
+          <t>Analytics Engineer, Day Shift, Strategic Analytics</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Confie</t>
+          <t>Adventist HealthCare</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Airflow, Python</t>
+          <t>EMR, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=049826f47ea60f4d</t>
+          <t>https://www.indeed.com/viewjob?jk=fc034fd3ef508e12</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>GenAI Python Systems Engineer – Experienced Associate</t>
+          <t>Senior UX Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Terraform, AWS CloudFormation, Docker, Python</t>
+          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=092180f6fccecac1</t>
+          <t>https://www.indeed.com/viewjob?jk=188385fe594d1176</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Analytics Engineer, Day Shift, Strategic Analytics</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Adventist HealthCare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>EMR, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc034fd3ef508e12</t>
+          <t>https://www.indeed.com/viewjob?jk=08083d178d541b5c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior UX Software Engineer</t>
+          <t>IT Systems Engineer III</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GRVTY</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Palm Beach Gardens, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,17 +3076,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, PostgreSQL, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=188385fe594d1176</t>
+          <t>https://www.indeed.com/viewjob?jk=371bf76528aae202</t>
         </is>
       </c>
     </row>
@@ -3128,17 +3128,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Advanced Systems Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>ConnectWise</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,120 +3146,15 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, Oracle, MySQL, NoSQL, ETL, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec9b8320959ff15</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=08083d178d541b5c</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>IT Systems Engineer III</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Delan Associates, Inc</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Palm Beach Gardens, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, PostgreSQL, ETL, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=371bf76528aae202</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Advanced Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>ConnectWise</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a6fd8dee63599f0d</t>
         </is>
